--- a/app/Archivos/Template/Template_HRC_Cenco.xlsx
+++ b/app/Archivos/Template/Template_HRC_Cenco.xlsx
@@ -626,35 +626,23 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>PMP1264114</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>151.3599999413127</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>1626994</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>151.3599999413127</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>1626994</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="C20" s="10" t="inlineStr">
@@ -664,16 +652,16 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>PMP1264114</t>
+          <t>PMP1266600</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1626994</v>
+        <v>7681336</v>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>1626994</v>
+        <v>7681336</v>
       </c>
       <c r="I20" s="11" t="inlineStr"/>
     </row>
@@ -685,16 +673,16 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>PMP1266600</t>
+          <t>PMP1266606</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>7681336</v>
+        <v>1192925</v>
       </c>
       <c r="F21" s="10" t="inlineStr"/>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>7681336</v>
+        <v>1192925</v>
       </c>
       <c r="I21" s="11" t="inlineStr"/>
     </row>
@@ -706,16 +694,16 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>PMP1266606</t>
+          <t>PMP1266608</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1192925</v>
+        <v>515675</v>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
       <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>1192925</v>
+        <v>515675</v>
       </c>
       <c r="I22" s="11" t="inlineStr"/>
     </row>
@@ -727,16 +715,16 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PMP1266608</t>
+          <t>PMP1266609</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>515675</v>
+        <v>1056161</v>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="6" t="n">
-        <v>515675</v>
+        <v>1056161</v>
       </c>
       <c r="I23" s="11" t="inlineStr"/>
     </row>
@@ -748,16 +736,16 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>PMP1266609</t>
+          <t>PMP1266649</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1056161</v>
+        <v>4590952</v>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
       <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="6" t="n">
-        <v>1056161</v>
+        <v>4590952</v>
       </c>
       <c r="I24" s="11" t="inlineStr"/>
     </row>
@@ -769,16 +757,16 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>PMP1266649</t>
+          <t>PMP1266654</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4590952</v>
+        <v>6861052</v>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
       <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>4590952</v>
+        <v>6861052</v>
       </c>
       <c r="I25" s="11" t="inlineStr"/>
     </row>
@@ -790,16 +778,16 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>PMP1266654</t>
+          <t>PMP1266655</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>6861052</v>
+        <v>1354633</v>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="6" t="n">
-        <v>6861052</v>
+        <v>1354633</v>
       </c>
       <c r="I26" s="11" t="inlineStr"/>
     </row>
@@ -811,16 +799,16 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PMP1266655</t>
+          <t>PMP1266658</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1354633</v>
+        <v>9803513</v>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>1354633</v>
+        <v>9803513</v>
       </c>
       <c r="I27" s="11" t="inlineStr"/>
     </row>
@@ -832,16 +820,16 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>PMP1266658</t>
+          <t>PMP1266661</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>9803513</v>
+        <v>1569283</v>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
       <c r="G28" s="10" t="inlineStr"/>
       <c r="H28" s="6" t="n">
-        <v>9803513</v>
+        <v>1569283</v>
       </c>
       <c r="I28" s="11" t="inlineStr"/>
     </row>
@@ -853,16 +841,16 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>PMP1266661</t>
+          <t>PMP1266687</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>1569283</v>
+        <v>12926095</v>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
       <c r="G29" s="10" t="inlineStr"/>
       <c r="H29" s="6" t="n">
-        <v>1569283</v>
+        <v>12926095</v>
       </c>
       <c r="I29" s="11" t="inlineStr"/>
     </row>
@@ -874,16 +862,16 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>PMP1266687</t>
+          <t>PMP1266688</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>12926095</v>
+        <v>14001409</v>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
       <c r="G30" s="10" t="inlineStr"/>
       <c r="H30" s="6" t="n">
-        <v>12926095</v>
+        <v>14001409</v>
       </c>
       <c r="I30" s="11" t="inlineStr"/>
     </row>
@@ -895,16 +883,16 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>PMP1266688</t>
+          <t>PMP1266722</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>14001409</v>
+        <v>2245916</v>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr"/>
       <c r="H31" s="6" t="n">
-        <v>14001409</v>
+        <v>2245916</v>
       </c>
       <c r="I31" s="11" t="inlineStr"/>
     </row>
@@ -916,16 +904,16 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>PMP1266722</t>
+          <t>PMP1266723</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2245916</v>
+        <v>14015891</v>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
       <c r="G32" s="10" t="inlineStr"/>
       <c r="H32" s="6" t="n">
-        <v>2245916</v>
+        <v>14015891</v>
       </c>
       <c r="I32" s="11" t="inlineStr"/>
     </row>
@@ -937,16 +925,16 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PMP1266723</t>
+          <t>PMP1266724</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>14015891</v>
+        <v>1719997</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>14015891</v>
+        <v>1719997</v>
       </c>
       <c r="I33" s="11" t="inlineStr"/>
     </row>
@@ -958,16 +946,16 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>PMP1266724</t>
+          <t>PMP1266725</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1719997</v>
+        <v>4736233</v>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="6" t="n">
-        <v>1719997</v>
+        <v>4736233</v>
       </c>
       <c r="I34" s="11" t="inlineStr"/>
     </row>
@@ -979,16 +967,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>PMP1266725</t>
+          <t>PMP1266726</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>4736233</v>
+        <v>3461094</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>4736233</v>
+        <v>3461094</v>
       </c>
       <c r="I35" s="11" t="inlineStr"/>
     </row>
@@ -1000,16 +988,16 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>PMP1266726</t>
+          <t>PMP1266727</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>3461094</v>
+        <v>1182498</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>3461094</v>
+        <v>1182498</v>
       </c>
       <c r="I36" s="11" t="inlineStr"/>
     </row>
@@ -1021,16 +1009,16 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>PMP1266727</t>
+          <t>PMP1266823</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1182498</v>
+        <v>8421580</v>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr"/>
       <c r="H37" s="6" t="n">
-        <v>1182498</v>
+        <v>8421580</v>
       </c>
       <c r="I37" s="11" t="inlineStr"/>
     </row>
@@ -1042,16 +1030,16 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>PMP1266823</t>
+          <t>PMP1266824</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>8421580</v>
+        <v>26241375</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>8421580</v>
+        <v>26241375</v>
       </c>
       <c r="I38" s="11" t="inlineStr"/>
     </row>
@@ -1063,16 +1051,16 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PMP1266824</t>
+          <t>PMP1266825</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>26241375</v>
+        <v>239794814</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>26241375</v>
+        <v>239794814</v>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
     </row>
@@ -1084,16 +1072,16 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>PMP1266825</t>
+          <t>PMP1266827</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>239794814</v>
+        <v>47671025</v>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>239794814</v>
+        <v>47671025</v>
       </c>
       <c r="I40" s="11" t="inlineStr"/>
     </row>
@@ -1105,16 +1093,16 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>PMP1266827</t>
+          <t>PMP1266963</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>47671025</v>
+        <v>47694293</v>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="10" t="inlineStr"/>
       <c r="H41" s="6" t="n">
-        <v>47671025</v>
+        <v>47694293</v>
       </c>
       <c r="I41" s="11" t="inlineStr"/>
     </row>
@@ -1126,16 +1114,16 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>PMP1266963</t>
+          <t>PMP1266964</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>47694293</v>
+        <v>29579477</v>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
       <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="6" t="n">
-        <v>47694293</v>
+        <v>29579477</v>
       </c>
       <c r="I42" s="11" t="inlineStr"/>
     </row>
@@ -1147,16 +1135,16 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>PMP1266964</t>
+          <t>PMP1266965</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>29579477</v>
+        <v>1382118</v>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
       <c r="G43" s="10" t="inlineStr"/>
       <c r="H43" s="6" t="n">
-        <v>29579477</v>
+        <v>1382118</v>
       </c>
       <c r="I43" s="11" t="inlineStr"/>
     </row>
@@ -1168,16 +1156,16 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>PMP1266965</t>
+          <t>PMP1266966</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1382118</v>
+        <v>21102985</v>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="6" t="n">
-        <v>1382118</v>
+        <v>21102985</v>
       </c>
       <c r="I44" s="11" t="inlineStr"/>
     </row>
@@ -1189,16 +1177,16 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>PMP1266966</t>
+          <t>PMP1266967</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>21102985</v>
+        <v>91081</v>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
       <c r="G45" s="10" t="inlineStr"/>
       <c r="H45" s="6" t="n">
-        <v>21102985</v>
+        <v>91081</v>
       </c>
       <c r="I45" s="11" t="inlineStr"/>
     </row>
@@ -1210,16 +1198,16 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>PMP1266967</t>
+          <t>PMP1266968</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>91081</v>
+        <v>40167191</v>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
       <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="6" t="n">
-        <v>91081</v>
+        <v>40167191</v>
       </c>
       <c r="I46" s="11" t="inlineStr"/>
     </row>
@@ -1231,16 +1219,16 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>PMP1266968</t>
+          <t>PMP1266969</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>40167191</v>
+        <v>9601461</v>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
       <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="6" t="n">
-        <v>40167191</v>
+        <v>9601461</v>
       </c>
       <c r="I47" s="11" t="inlineStr"/>
     </row>
@@ -1252,16 +1240,16 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>PMP1266969</t>
+          <t>PMP1266970</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>9601461</v>
+        <v>644999</v>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="6" t="n">
-        <v>9601461</v>
+        <v>644999</v>
       </c>
       <c r="I48" s="11" t="inlineStr"/>
     </row>
@@ -1273,16 +1261,16 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>PMP1266970</t>
+          <t>PMP1266971</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>644999</v>
+        <v>5282722</v>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="6" t="n">
-        <v>644999</v>
+        <v>5282722</v>
       </c>
       <c r="I49" s="11" t="inlineStr"/>
     </row>
@@ -1294,16 +1282,16 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>PMP1266971</t>
+          <t>PMP1266972</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>5282722</v>
+        <v>156976207</v>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
       <c r="G50" s="10" t="inlineStr"/>
       <c r="H50" s="6" t="n">
-        <v>5282722</v>
+        <v>156976207</v>
       </c>
       <c r="I50" s="11" t="inlineStr"/>
     </row>
@@ -1315,16 +1303,16 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>PMP1266972</t>
+          <t>PMP1266973</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>156976207</v>
+        <v>2402351</v>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="10" t="inlineStr"/>
       <c r="H51" s="6" t="n">
-        <v>156976207</v>
+        <v>2402351</v>
       </c>
       <c r="I51" s="11" t="inlineStr"/>
     </row>
@@ -1336,16 +1324,16 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>PMP1266973</t>
+          <t>PMP1266974</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>2402351</v>
+        <v>2094872</v>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
       <c r="G52" s="10" t="inlineStr"/>
       <c r="H52" s="6" t="n">
-        <v>2402351</v>
+        <v>2094872</v>
       </c>
       <c r="I52" s="11" t="inlineStr"/>
     </row>
@@ -1357,16 +1345,16 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>PMP1266974</t>
+          <t>PMP1266975</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>2094872</v>
+        <v>12981428</v>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
       <c r="G53" s="10" t="inlineStr"/>
       <c r="H53" s="6" t="n">
-        <v>2094872</v>
+        <v>12981428</v>
       </c>
       <c r="I53" s="11" t="inlineStr"/>
     </row>
@@ -1378,16 +1366,16 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>PMP1266975</t>
+          <t>PMP1266976</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>12981428</v>
+        <v>21995834</v>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
       <c r="G54" s="10" t="inlineStr"/>
       <c r="H54" s="6" t="n">
-        <v>12981428</v>
+        <v>21995834</v>
       </c>
       <c r="I54" s="11" t="inlineStr"/>
     </row>
@@ -1399,16 +1387,16 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>PMP1266976</t>
+          <t>PMP1266977</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>21995834</v>
+        <v>3902494</v>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="6" t="n">
-        <v>21995834</v>
+        <v>3902494</v>
       </c>
       <c r="I55" s="11" t="inlineStr"/>
     </row>
@@ -1420,16 +1408,16 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>PMP1266977</t>
+          <t>PMP1266978</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>3902494</v>
+        <v>68246480</v>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
       <c r="G56" s="10" t="inlineStr"/>
       <c r="H56" s="6" t="n">
-        <v>3902494</v>
+        <v>68246480</v>
       </c>
       <c r="I56" s="11" t="inlineStr"/>
     </row>
@@ -1441,16 +1429,16 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>PMP1266978</t>
+          <t>PMP1266979</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>68246480</v>
+        <v>5762055</v>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
       <c r="G57" s="10" t="inlineStr"/>
       <c r="H57" s="6" t="n">
-        <v>68246480</v>
+        <v>5762055</v>
       </c>
       <c r="I57" s="11" t="inlineStr"/>
     </row>
@@ -1462,16 +1450,16 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>PMP1266979</t>
+          <t>PMP1266980</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>5762055</v>
+        <v>1286570</v>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr"/>
       <c r="H58" s="6" t="n">
-        <v>5762055</v>
+        <v>1286570</v>
       </c>
       <c r="I58" s="11" t="inlineStr"/>
     </row>
@@ -1483,16 +1471,16 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>PMP1266980</t>
+          <t>PMP1267003</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1286570</v>
+        <v>639553</v>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
       <c r="G59" s="10" t="inlineStr"/>
       <c r="H59" s="6" t="n">
-        <v>1286570</v>
+        <v>639553</v>
       </c>
       <c r="I59" s="11" t="inlineStr"/>
     </row>
@@ -1504,16 +1492,16 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>PMP1267003</t>
+          <t>PMP1267004</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>639553</v>
+        <v>84944511</v>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
       <c r="G60" s="10" t="inlineStr"/>
       <c r="H60" s="6" t="n">
-        <v>639553</v>
+        <v>84944511</v>
       </c>
       <c r="I60" s="11" t="inlineStr"/>
     </row>
@@ -1525,16 +1513,16 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>PMP1267004</t>
+          <t>PMP1267005</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>84944511</v>
+        <v>49983694</v>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
       <c r="G61" s="10" t="inlineStr"/>
       <c r="H61" s="6" t="n">
-        <v>84944511</v>
+        <v>49983694</v>
       </c>
       <c r="I61" s="11" t="inlineStr"/>
     </row>
@@ -1546,16 +1534,16 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>PMP1267005</t>
+          <t>PMP1267006</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>49983694</v>
+        <v>19199898</v>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
       <c r="G62" s="10" t="inlineStr"/>
       <c r="H62" s="6" t="n">
-        <v>49983694</v>
+        <v>19199898</v>
       </c>
       <c r="I62" s="11" t="inlineStr"/>
     </row>
@@ -1567,16 +1555,16 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>PMP1267006</t>
+          <t>PMP1267007</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>19199898</v>
+        <v>182163</v>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
       <c r="G63" s="10" t="inlineStr"/>
       <c r="H63" s="6" t="n">
-        <v>19199898</v>
+        <v>182163</v>
       </c>
       <c r="I63" s="11" t="inlineStr"/>
     </row>
@@ -1588,16 +1576,16 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>PMP1267007</t>
+          <t>PMP1267008</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>182163</v>
+        <v>2257497</v>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
       <c r="G64" s="10" t="inlineStr"/>
       <c r="H64" s="6" t="n">
-        <v>182163</v>
+        <v>2257497</v>
       </c>
       <c r="I64" s="11" t="inlineStr"/>
     </row>
@@ -1609,16 +1597,16 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>PMP1267008</t>
+          <t>PMP1267040</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>2257497</v>
+        <v>4073613</v>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
       <c r="G65" s="10" t="inlineStr"/>
       <c r="H65" s="6" t="n">
-        <v>2257497</v>
+        <v>4073613</v>
       </c>
       <c r="I65" s="11" t="inlineStr"/>
     </row>
@@ -1630,16 +1618,16 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>PMP1267040</t>
+          <t>PMP1267041</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>4073613</v>
+        <v>87870163</v>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
       <c r="G66" s="10" t="inlineStr"/>
       <c r="H66" s="6" t="n">
-        <v>4073613</v>
+        <v>87870163</v>
       </c>
       <c r="I66" s="11" t="inlineStr"/>
     </row>
@@ -1651,16 +1639,16 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>PMP1267041</t>
+          <t>PMP1267042</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>87870163</v>
+        <v>106410136</v>
       </c>
       <c r="F67" s="10" t="inlineStr"/>
       <c r="G67" s="10" t="inlineStr"/>
       <c r="H67" s="6" t="n">
-        <v>87870163</v>
+        <v>106410136</v>
       </c>
       <c r="I67" s="11" t="inlineStr"/>
     </row>
@@ -1672,16 +1660,16 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>PMP1267042</t>
+          <t>PMP1267043</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>106410136</v>
+        <v>67330086</v>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
       <c r="G68" s="10" t="inlineStr"/>
       <c r="H68" s="6" t="n">
-        <v>106410136</v>
+        <v>67330086</v>
       </c>
       <c r="I68" s="11" t="inlineStr"/>
     </row>
@@ -1693,16 +1681,16 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>PMP1267043</t>
+          <t>PMP1267044</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>67330086</v>
+        <v>4918396</v>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
       <c r="G69" s="10" t="inlineStr"/>
       <c r="H69" s="6" t="n">
-        <v>67330086</v>
+        <v>4918396</v>
       </c>
       <c r="I69" s="11" t="inlineStr"/>
     </row>
@@ -1714,16 +1702,16 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>PMP1267044</t>
+          <t>PMP1267045</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>4918396</v>
+        <v>1275140</v>
       </c>
       <c r="F70" s="10" t="inlineStr"/>
       <c r="G70" s="10" t="inlineStr"/>
       <c r="H70" s="6" t="n">
-        <v>4918396</v>
+        <v>1275140</v>
       </c>
       <c r="I70" s="11" t="inlineStr"/>
     </row>
@@ -1735,16 +1723,16 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>PMP1267045</t>
+          <t>PMP1267186</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1275140</v>
+        <v>46847802</v>
       </c>
       <c r="F71" s="10" t="inlineStr"/>
       <c r="G71" s="10" t="inlineStr"/>
       <c r="H71" s="6" t="n">
-        <v>1275140</v>
+        <v>46847802</v>
       </c>
       <c r="I71" s="11" t="inlineStr"/>
     </row>
@@ -1756,16 +1744,16 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>PMP1267186</t>
+          <t>PMP1267187</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>46847802</v>
+        <v>8031748</v>
       </c>
       <c r="F72" s="10" t="inlineStr"/>
       <c r="G72" s="10" t="inlineStr"/>
       <c r="H72" s="6" t="n">
-        <v>46847802</v>
+        <v>8031748</v>
       </c>
       <c r="I72" s="11" t="inlineStr"/>
     </row>
@@ -1777,16 +1765,16 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>PMP1267187</t>
+          <t>PMP1267188</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>8031748</v>
+        <v>162389699</v>
       </c>
       <c r="F73" s="10" t="inlineStr"/>
       <c r="G73" s="10" t="inlineStr"/>
       <c r="H73" s="6" t="n">
-        <v>8031748</v>
+        <v>162389699</v>
       </c>
       <c r="I73" s="11" t="inlineStr"/>
     </row>
@@ -1798,16 +1786,16 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>PMP1267188</t>
+          <t>PMP1267189</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>162389699</v>
+        <v>34317772</v>
       </c>
       <c r="F74" s="10" t="inlineStr"/>
       <c r="G74" s="10" t="inlineStr"/>
       <c r="H74" s="6" t="n">
-        <v>162389699</v>
+        <v>34317772</v>
       </c>
       <c r="I74" s="11" t="inlineStr"/>
     </row>
@@ -1819,16 +1807,16 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>PMP1267189</t>
+          <t>PMP1267301</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>34317772</v>
+        <v>5565499</v>
       </c>
       <c r="F75" s="10" t="inlineStr"/>
       <c r="G75" s="10" t="inlineStr"/>
       <c r="H75" s="6" t="n">
-        <v>34317772</v>
+        <v>5565499</v>
       </c>
       <c r="I75" s="11" t="inlineStr"/>
     </row>
@@ -1840,16 +1828,16 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>PMP1267301</t>
+          <t>PMP1267303</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>5565499</v>
+        <v>4021792</v>
       </c>
       <c r="F76" s="10" t="inlineStr"/>
       <c r="G76" s="10" t="inlineStr"/>
       <c r="H76" s="6" t="n">
-        <v>5565499</v>
+        <v>4021792</v>
       </c>
       <c r="I76" s="11" t="inlineStr"/>
     </row>
@@ -1861,16 +1849,16 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>PMP1267303</t>
+          <t>PMP1267309</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>4021792</v>
+        <v>7647025</v>
       </c>
       <c r="F77" s="10" t="inlineStr"/>
       <c r="G77" s="10" t="inlineStr"/>
       <c r="H77" s="6" t="n">
-        <v>4021792</v>
+        <v>7647025</v>
       </c>
       <c r="I77" s="11" t="inlineStr"/>
     </row>
@@ -1882,16 +1870,16 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>PMP1267309</t>
+          <t>PMP1267318</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>7647025</v>
+        <v>46502524</v>
       </c>
       <c r="F78" s="10" t="inlineStr"/>
       <c r="G78" s="10" t="inlineStr"/>
       <c r="H78" s="6" t="n">
-        <v>7647025</v>
+        <v>46502524</v>
       </c>
       <c r="I78" s="11" t="inlineStr"/>
     </row>
@@ -1903,16 +1891,16 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>PMP1267318</t>
+          <t>PMP1267319</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>46502524</v>
+        <v>1213908</v>
       </c>
       <c r="F79" s="10" t="inlineStr"/>
       <c r="G79" s="10" t="inlineStr"/>
       <c r="H79" s="6" t="n">
-        <v>46502524</v>
+        <v>1213908</v>
       </c>
       <c r="I79" s="11" t="inlineStr"/>
     </row>
@@ -1924,16 +1912,16 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>PMP1267319</t>
+          <t>PMP1267320</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1213908</v>
+        <v>4354949</v>
       </c>
       <c r="F80" s="10" t="inlineStr"/>
       <c r="G80" s="10" t="inlineStr"/>
       <c r="H80" s="6" t="n">
-        <v>1213908</v>
+        <v>4354949</v>
       </c>
       <c r="I80" s="11" t="inlineStr"/>
     </row>
@@ -1945,16 +1933,16 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>PMP1267320</t>
+          <t>PMP1267321</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>4354949</v>
+        <v>5068919</v>
       </c>
       <c r="F81" s="10" t="inlineStr"/>
       <c r="G81" s="10" t="inlineStr"/>
       <c r="H81" s="6" t="n">
-        <v>4354949</v>
+        <v>5068919</v>
       </c>
       <c r="I81" s="11" t="inlineStr"/>
     </row>
@@ -1966,16 +1954,16 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>PMP1267321</t>
+          <t>PMP1267438</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>5068919</v>
+        <v>210520048</v>
       </c>
       <c r="F82" s="10" t="inlineStr"/>
       <c r="G82" s="10" t="inlineStr"/>
       <c r="H82" s="6" t="n">
-        <v>5068919</v>
+        <v>210520048</v>
       </c>
       <c r="I82" s="11" t="inlineStr"/>
     </row>
@@ -1987,16 +1975,16 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>PMP1267438</t>
+          <t>PMP1267439</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>210520048</v>
+        <v>116838564</v>
       </c>
       <c r="F83" s="10" t="inlineStr"/>
       <c r="G83" s="10" t="inlineStr"/>
       <c r="H83" s="6" t="n">
-        <v>210520048</v>
+        <v>116838564</v>
       </c>
       <c r="I83" s="11" t="inlineStr"/>
     </row>
@@ -2008,16 +1996,16 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>PMP1267439</t>
+          <t>PMP1267583</t>
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>116838564</v>
+        <v>122639804</v>
       </c>
       <c r="F84" s="10" t="inlineStr"/>
       <c r="G84" s="10" t="inlineStr"/>
       <c r="H84" s="6" t="n">
-        <v>116838564</v>
+        <v>122639804</v>
       </c>
       <c r="I84" s="11" t="inlineStr"/>
     </row>
@@ -2029,16 +2017,16 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>PMP1267583</t>
+          <t>PMP1267584</t>
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>122639804</v>
+        <v>154180817</v>
       </c>
       <c r="F85" s="10" t="inlineStr"/>
       <c r="G85" s="10" t="inlineStr"/>
       <c r="H85" s="6" t="n">
-        <v>122639804</v>
+        <v>154180817</v>
       </c>
       <c r="I85" s="11" t="inlineStr"/>
     </row>
@@ -2050,16 +2038,16 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>PMP1267584</t>
+          <t>PMP1267585</t>
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>154180817</v>
+        <v>8467845</v>
       </c>
       <c r="F86" s="10" t="inlineStr"/>
       <c r="G86" s="10" t="inlineStr"/>
       <c r="H86" s="6" t="n">
-        <v>154180817</v>
+        <v>8467845</v>
       </c>
       <c r="I86" s="11" t="inlineStr"/>
     </row>
@@ -2071,16 +2059,16 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>PMP1267585</t>
+          <t>PMP1267631</t>
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>8467845</v>
+        <v>400238570</v>
       </c>
       <c r="F87" s="10" t="inlineStr"/>
       <c r="G87" s="10" t="inlineStr"/>
       <c r="H87" s="6" t="n">
-        <v>8467845</v>
+        <v>400238570</v>
       </c>
       <c r="I87" s="11" t="inlineStr"/>
     </row>
@@ -2092,16 +2080,16 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>PMP1267631</t>
+          <t>PMP1268022</t>
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>400238570</v>
+        <v>2886409</v>
       </c>
       <c r="F88" s="10" t="inlineStr"/>
       <c r="G88" s="10" t="inlineStr"/>
       <c r="H88" s="6" t="n">
-        <v>400238570</v>
+        <v>2886409</v>
       </c>
       <c r="I88" s="11" t="inlineStr"/>
     </row>
@@ -2113,16 +2101,16 @@
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>PMP1268022</t>
+          <t>PMP1268023</t>
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>2886409</v>
+        <v>7320998</v>
       </c>
       <c r="F89" s="10" t="inlineStr"/>
       <c r="G89" s="10" t="inlineStr"/>
       <c r="H89" s="6" t="n">
-        <v>2886409</v>
+        <v>7320998</v>
       </c>
       <c r="I89" s="11" t="inlineStr"/>
     </row>
@@ -2134,16 +2122,16 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>PMP1268023</t>
+          <t>PMP1268024</t>
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>7320998</v>
+        <v>34246890</v>
       </c>
       <c r="F90" s="10" t="inlineStr"/>
       <c r="G90" s="10" t="inlineStr"/>
       <c r="H90" s="6" t="n">
-        <v>7320998</v>
+        <v>34246890</v>
       </c>
       <c r="I90" s="11" t="inlineStr"/>
     </row>
@@ -2155,16 +2143,16 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>PMP1268024</t>
+          <t>PMP1268025</t>
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>34246890</v>
+        <v>23587956</v>
       </c>
       <c r="F91" s="10" t="inlineStr"/>
       <c r="G91" s="10" t="inlineStr"/>
       <c r="H91" s="6" t="n">
-        <v>34246890</v>
+        <v>23587956</v>
       </c>
       <c r="I91" s="11" t="inlineStr"/>
     </row>
@@ -2176,16 +2164,16 @@
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>PMP1268025</t>
+          <t>PMP1268026</t>
         </is>
       </c>
       <c r="E92" s="6" t="n">
-        <v>23587956</v>
+        <v>1832981</v>
       </c>
       <c r="F92" s="10" t="inlineStr"/>
       <c r="G92" s="10" t="inlineStr"/>
       <c r="H92" s="6" t="n">
-        <v>23587956</v>
+        <v>1832981</v>
       </c>
       <c r="I92" s="11" t="inlineStr"/>
     </row>
@@ -2197,16 +2185,16 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>PMP1268026</t>
+          <t>PMP1268027</t>
         </is>
       </c>
       <c r="E93" s="6" t="n">
-        <v>1832981</v>
+        <v>82091603</v>
       </c>
       <c r="F93" s="10" t="inlineStr"/>
       <c r="G93" s="10" t="inlineStr"/>
       <c r="H93" s="6" t="n">
-        <v>1832981</v>
+        <v>82091603</v>
       </c>
       <c r="I93" s="11" t="inlineStr"/>
     </row>
@@ -2218,16 +2206,16 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>PMP1268027</t>
+          <t>PMP1268028</t>
         </is>
       </c>
       <c r="E94" s="6" t="n">
-        <v>82091603</v>
+        <v>96101782</v>
       </c>
       <c r="F94" s="10" t="inlineStr"/>
       <c r="G94" s="10" t="inlineStr"/>
       <c r="H94" s="6" t="n">
-        <v>82091603</v>
+        <v>96101782</v>
       </c>
       <c r="I94" s="11" t="inlineStr"/>
     </row>
@@ -2239,16 +2227,16 @@
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>PMP1268028</t>
+          <t>PMP1268029</t>
         </is>
       </c>
       <c r="E95" s="6" t="n">
-        <v>96101782</v>
+        <v>62894707</v>
       </c>
       <c r="F95" s="10" t="inlineStr"/>
       <c r="G95" s="10" t="inlineStr"/>
       <c r="H95" s="6" t="n">
-        <v>96101782</v>
+        <v>62894707</v>
       </c>
       <c r="I95" s="11" t="inlineStr"/>
     </row>
@@ -2260,16 +2248,16 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>PMP1268029</t>
+          <t>PMP1268030</t>
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>62894707</v>
+        <v>1366221</v>
       </c>
       <c r="F96" s="10" t="inlineStr"/>
       <c r="G96" s="10" t="inlineStr"/>
       <c r="H96" s="6" t="n">
-        <v>62894707</v>
+        <v>1366221</v>
       </c>
       <c r="I96" s="11" t="inlineStr"/>
     </row>
@@ -2281,16 +2269,16 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>PMP1268030</t>
+          <t>PMP1268608</t>
         </is>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1366221</v>
+        <v>318736853</v>
       </c>
       <c r="F97" s="10" t="inlineStr"/>
       <c r="G97" s="10" t="inlineStr"/>
       <c r="H97" s="6" t="n">
-        <v>1366221</v>
+        <v>318736853</v>
       </c>
       <c r="I97" s="11" t="inlineStr"/>
     </row>
@@ -2302,16 +2290,16 @@
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>PMP1268608</t>
+          <t>PMP1268642</t>
         </is>
       </c>
       <c r="E98" s="6" t="n">
-        <v>318736853</v>
+        <v>247763468</v>
       </c>
       <c r="F98" s="10" t="inlineStr"/>
       <c r="G98" s="10" t="inlineStr"/>
       <c r="H98" s="6" t="n">
-        <v>318736853</v>
+        <v>247763468</v>
       </c>
       <c r="I98" s="11" t="inlineStr"/>
     </row>
@@ -2323,16 +2311,16 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>PMP1268642</t>
+          <t>PMP1268643</t>
         </is>
       </c>
       <c r="E99" s="6" t="n">
-        <v>247763468</v>
+        <v>306335700</v>
       </c>
       <c r="F99" s="10" t="inlineStr"/>
       <c r="G99" s="10" t="inlineStr"/>
       <c r="H99" s="6" t="n">
-        <v>247763468</v>
+        <v>306335700</v>
       </c>
       <c r="I99" s="11" t="inlineStr"/>
     </row>
@@ -2344,16 +2332,16 @@
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>PMP1268643</t>
+          <t>PMP1268644</t>
         </is>
       </c>
       <c r="E100" s="6" t="n">
-        <v>306335700</v>
+        <v>193389687</v>
       </c>
       <c r="F100" s="10" t="inlineStr"/>
       <c r="G100" s="10" t="inlineStr"/>
       <c r="H100" s="6" t="n">
-        <v>306335700</v>
+        <v>193389687</v>
       </c>
       <c r="I100" s="11" t="inlineStr"/>
     </row>
@@ -2365,16 +2353,16 @@
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>PMP1268644</t>
+          <t>PMP1268645</t>
         </is>
       </c>
       <c r="E101" s="6" t="n">
-        <v>193389687</v>
+        <v>150574059</v>
       </c>
       <c r="F101" s="10" t="inlineStr"/>
       <c r="G101" s="10" t="inlineStr"/>
       <c r="H101" s="6" t="n">
-        <v>193389687</v>
+        <v>150574059</v>
       </c>
       <c r="I101" s="11" t="inlineStr"/>
     </row>
@@ -2386,16 +2374,16 @@
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>PMP1268645</t>
+          <t>PMP1268714</t>
         </is>
       </c>
       <c r="E102" s="6" t="n">
-        <v>150574059</v>
+        <v>137182641</v>
       </c>
       <c r="F102" s="10" t="inlineStr"/>
       <c r="G102" s="10" t="inlineStr"/>
       <c r="H102" s="6" t="n">
-        <v>150574059</v>
+        <v>137182641</v>
       </c>
       <c r="I102" s="11" t="inlineStr"/>
     </row>
@@ -2407,16 +2395,16 @@
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>PMP1268714</t>
+          <t>PMP1268715</t>
         </is>
       </c>
       <c r="E103" s="6" t="n">
-        <v>137182641</v>
+        <v>121147307</v>
       </c>
       <c r="F103" s="10" t="inlineStr"/>
       <c r="G103" s="10" t="inlineStr"/>
       <c r="H103" s="6" t="n">
-        <v>137182641</v>
+        <v>121147307</v>
       </c>
       <c r="I103" s="11" t="inlineStr"/>
     </row>
@@ -2428,16 +2416,16 @@
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>PMP1268715</t>
+          <t>PMP1268740</t>
         </is>
       </c>
       <c r="E104" s="6" t="n">
-        <v>121147307</v>
+        <v>66622142</v>
       </c>
       <c r="F104" s="10" t="inlineStr"/>
       <c r="G104" s="10" t="inlineStr"/>
       <c r="H104" s="6" t="n">
-        <v>121147307</v>
+        <v>66622142</v>
       </c>
       <c r="I104" s="11" t="inlineStr"/>
     </row>
@@ -2449,16 +2437,16 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>PMP1268740</t>
+          <t>PMP1268745</t>
         </is>
       </c>
       <c r="E105" s="6" t="n">
-        <v>66622142</v>
+        <v>10451906</v>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
       <c r="G105" s="10" t="inlineStr"/>
       <c r="H105" s="6" t="n">
-        <v>66622142</v>
+        <v>10451906</v>
       </c>
       <c r="I105" s="11" t="inlineStr"/>
     </row>
@@ -2470,16 +2458,16 @@
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>PMP1268745</t>
+          <t>PMP1268746</t>
         </is>
       </c>
       <c r="E106" s="6" t="n">
-        <v>10451906</v>
+        <v>2743164</v>
       </c>
       <c r="F106" s="10" t="inlineStr"/>
       <c r="G106" s="10" t="inlineStr"/>
       <c r="H106" s="6" t="n">
-        <v>10451906</v>
+        <v>2743164</v>
       </c>
       <c r="I106" s="11" t="inlineStr"/>
     </row>
@@ -2491,16 +2479,16 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>PMP1268746</t>
+          <t>PMP1268747</t>
         </is>
       </c>
       <c r="E107" s="6" t="n">
-        <v>2743164</v>
+        <v>1315849</v>
       </c>
       <c r="F107" s="10" t="inlineStr"/>
       <c r="G107" s="10" t="inlineStr"/>
       <c r="H107" s="6" t="n">
-        <v>2743164</v>
+        <v>1315849</v>
       </c>
       <c r="I107" s="11" t="inlineStr"/>
     </row>
@@ -2512,16 +2500,16 @@
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>PMP1268747</t>
+          <t>PMP1268751</t>
         </is>
       </c>
       <c r="E108" s="6" t="n">
-        <v>1315849</v>
+        <v>4422869</v>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
       <c r="G108" s="10" t="inlineStr"/>
       <c r="H108" s="6" t="n">
-        <v>1315849</v>
+        <v>4422869</v>
       </c>
       <c r="I108" s="11" t="inlineStr"/>
     </row>
@@ -2533,16 +2521,16 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>PMP1268751</t>
+          <t>PMP1268752</t>
         </is>
       </c>
       <c r="E109" s="6" t="n">
-        <v>4422869</v>
+        <v>66343032</v>
       </c>
       <c r="F109" s="10" t="inlineStr"/>
       <c r="G109" s="10" t="inlineStr"/>
       <c r="H109" s="6" t="n">
-        <v>4422869</v>
+        <v>66343032</v>
       </c>
       <c r="I109" s="11" t="inlineStr"/>
     </row>
@@ -2554,16 +2542,16 @@
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>PMP1268752</t>
+          <t>PMP1268753</t>
         </is>
       </c>
       <c r="E110" s="6" t="n">
-        <v>66343032</v>
+        <v>293119</v>
       </c>
       <c r="F110" s="10" t="inlineStr"/>
       <c r="G110" s="10" t="inlineStr"/>
       <c r="H110" s="6" t="n">
-        <v>66343032</v>
+        <v>293119</v>
       </c>
       <c r="I110" s="11" t="inlineStr"/>
     </row>
@@ -2575,16 +2563,16 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>PMP1268753</t>
+          <t>PMP1268754</t>
         </is>
       </c>
       <c r="E111" s="6" t="n">
-        <v>293119</v>
+        <v>871150</v>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
       <c r="G111" s="10" t="inlineStr"/>
       <c r="H111" s="6" t="n">
-        <v>293119</v>
+        <v>871150</v>
       </c>
       <c r="I111" s="11" t="inlineStr"/>
     </row>
@@ -2596,16 +2584,16 @@
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>PMP1268754</t>
+          <t>PMP1268758</t>
         </is>
       </c>
       <c r="E112" s="6" t="n">
-        <v>871150</v>
+        <v>9059735</v>
       </c>
       <c r="F112" s="10" t="inlineStr"/>
       <c r="G112" s="10" t="inlineStr"/>
       <c r="H112" s="6" t="n">
-        <v>871150</v>
+        <v>9059735</v>
       </c>
       <c r="I112" s="11" t="inlineStr"/>
     </row>
@@ -2617,16 +2605,16 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>PMP1268758</t>
+          <t>PMP1268759</t>
         </is>
       </c>
       <c r="E113" s="6" t="n">
-        <v>9059735</v>
+        <v>245799521</v>
       </c>
       <c r="F113" s="10" t="inlineStr"/>
       <c r="G113" s="10" t="inlineStr"/>
       <c r="H113" s="6" t="n">
-        <v>9059735</v>
+        <v>245799521</v>
       </c>
       <c r="I113" s="11" t="inlineStr"/>
     </row>
@@ -2638,16 +2626,16 @@
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>PMP1268759</t>
+          <t>PMP1269678</t>
         </is>
       </c>
       <c r="E114" s="6" t="n">
-        <v>245799521</v>
+        <v>9774576</v>
       </c>
       <c r="F114" s="10" t="inlineStr"/>
       <c r="G114" s="10" t="inlineStr"/>
       <c r="H114" s="6" t="n">
-        <v>245799521</v>
+        <v>9774576</v>
       </c>
       <c r="I114" s="11" t="inlineStr"/>
     </row>
@@ -2659,16 +2647,16 @@
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>PMP1269678</t>
+          <t>PMP1269679</t>
         </is>
       </c>
       <c r="E115" s="6" t="n">
-        <v>9774576</v>
+        <v>53195687</v>
       </c>
       <c r="F115" s="10" t="inlineStr"/>
       <c r="G115" s="10" t="inlineStr"/>
       <c r="H115" s="6" t="n">
-        <v>9774576</v>
+        <v>53195687</v>
       </c>
       <c r="I115" s="11" t="inlineStr"/>
     </row>
@@ -2680,16 +2668,16 @@
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>PMP1269679</t>
+          <t>PMP1269680</t>
         </is>
       </c>
       <c r="E116" s="6" t="n">
-        <v>53195687</v>
+        <v>259434738</v>
       </c>
       <c r="F116" s="10" t="inlineStr"/>
       <c r="G116" s="10" t="inlineStr"/>
       <c r="H116" s="6" t="n">
-        <v>53195687</v>
+        <v>259434738</v>
       </c>
       <c r="I116" s="11" t="inlineStr"/>
     </row>
@@ -2701,16 +2689,16 @@
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>PMP1269680</t>
+          <t>PMP1269681</t>
         </is>
       </c>
       <c r="E117" s="6" t="n">
-        <v>259434738</v>
+        <v>304785257</v>
       </c>
       <c r="F117" s="10" t="inlineStr"/>
       <c r="G117" s="10" t="inlineStr"/>
       <c r="H117" s="6" t="n">
-        <v>259434738</v>
+        <v>304785257</v>
       </c>
       <c r="I117" s="11" t="inlineStr"/>
     </row>
@@ -2722,16 +2710,16 @@
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>PMP1269681</t>
+          <t>PMP1269682</t>
         </is>
       </c>
       <c r="E118" s="6" t="n">
-        <v>304785257</v>
+        <v>247957487</v>
       </c>
       <c r="F118" s="10" t="inlineStr"/>
       <c r="G118" s="10" t="inlineStr"/>
       <c r="H118" s="6" t="n">
-        <v>304785257</v>
+        <v>247957487</v>
       </c>
       <c r="I118" s="11" t="inlineStr"/>
     </row>
@@ -2743,16 +2731,16 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>PMP1269682</t>
+          <t>PMP1269707</t>
         </is>
       </c>
       <c r="E119" s="6" t="n">
-        <v>247957487</v>
+        <v>1027679</v>
       </c>
       <c r="F119" s="10" t="inlineStr"/>
       <c r="G119" s="10" t="inlineStr"/>
       <c r="H119" s="6" t="n">
-        <v>247957487</v>
+        <v>1027679</v>
       </c>
       <c r="I119" s="11" t="inlineStr"/>
     </row>
@@ -2764,16 +2752,16 @@
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>PMP1269707</t>
+          <t>PMP1269708</t>
         </is>
       </c>
       <c r="E120" s="6" t="n">
-        <v>1027679</v>
+        <v>6267481</v>
       </c>
       <c r="F120" s="10" t="inlineStr"/>
       <c r="G120" s="10" t="inlineStr"/>
       <c r="H120" s="6" t="n">
-        <v>1027679</v>
+        <v>6267481</v>
       </c>
       <c r="I120" s="11" t="inlineStr"/>
     </row>
@@ -2785,16 +2773,16 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>PMP1269708</t>
+          <t>PMP1269709</t>
         </is>
       </c>
       <c r="E121" s="6" t="n">
-        <v>6267481</v>
+        <v>1687666</v>
       </c>
       <c r="F121" s="10" t="inlineStr"/>
       <c r="G121" s="10" t="inlineStr"/>
       <c r="H121" s="6" t="n">
-        <v>6267481</v>
+        <v>1687666</v>
       </c>
       <c r="I121" s="11" t="inlineStr"/>
     </row>
@@ -2806,16 +2794,16 @@
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>PMP1269709</t>
+          <t>PMP1269710</t>
         </is>
       </c>
       <c r="E122" s="6" t="n">
-        <v>1687666</v>
+        <v>1965612</v>
       </c>
       <c r="F122" s="10" t="inlineStr"/>
       <c r="G122" s="10" t="inlineStr"/>
       <c r="H122" s="6" t="n">
-        <v>1687666</v>
+        <v>1965612</v>
       </c>
       <c r="I122" s="11" t="inlineStr"/>
     </row>
@@ -2827,16 +2815,16 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>PMP1269710</t>
+          <t>PMP1269711</t>
         </is>
       </c>
       <c r="E123" s="6" t="n">
-        <v>1965612</v>
+        <v>1661332</v>
       </c>
       <c r="F123" s="10" t="inlineStr"/>
       <c r="G123" s="10" t="inlineStr"/>
       <c r="H123" s="6" t="n">
-        <v>1965612</v>
+        <v>1661332</v>
       </c>
       <c r="I123" s="11" t="inlineStr"/>
     </row>
@@ -2848,16 +2836,16 @@
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>PMP1269711</t>
+          <t>PMP1269712</t>
         </is>
       </c>
       <c r="E124" s="6" t="n">
-        <v>1661332</v>
+        <v>887680</v>
       </c>
       <c r="F124" s="10" t="inlineStr"/>
       <c r="G124" s="10" t="inlineStr"/>
       <c r="H124" s="6" t="n">
-        <v>1661332</v>
+        <v>887680</v>
       </c>
       <c r="I124" s="11" t="inlineStr"/>
     </row>
@@ -2869,16 +2857,16 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>PMP1269712</t>
+          <t>PMP1269723</t>
         </is>
       </c>
       <c r="E125" s="6" t="n">
-        <v>887680</v>
+        <v>1786295</v>
       </c>
       <c r="F125" s="10" t="inlineStr"/>
       <c r="G125" s="10" t="inlineStr"/>
       <c r="H125" s="6" t="n">
-        <v>887680</v>
+        <v>1786295</v>
       </c>
       <c r="I125" s="11" t="inlineStr"/>
     </row>
@@ -2890,16 +2878,16 @@
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>PMP1269723</t>
+          <t>PMP1269724</t>
         </is>
       </c>
       <c r="E126" s="6" t="n">
-        <v>1786295</v>
+        <v>1296269</v>
       </c>
       <c r="F126" s="10" t="inlineStr"/>
       <c r="G126" s="10" t="inlineStr"/>
       <c r="H126" s="6" t="n">
-        <v>1786295</v>
+        <v>1296269</v>
       </c>
       <c r="I126" s="11" t="inlineStr"/>
     </row>
@@ -2911,16 +2899,16 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>PMP1269724</t>
+          <t>PMP1269725</t>
         </is>
       </c>
       <c r="E127" s="6" t="n">
-        <v>1296269</v>
+        <v>5403419</v>
       </c>
       <c r="F127" s="10" t="inlineStr"/>
       <c r="G127" s="10" t="inlineStr"/>
       <c r="H127" s="6" t="n">
-        <v>1296269</v>
+        <v>5403419</v>
       </c>
       <c r="I127" s="11" t="inlineStr"/>
     </row>
@@ -2932,16 +2920,16 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>PMP1269725</t>
+          <t>PMP1269726</t>
         </is>
       </c>
       <c r="E128" s="6" t="n">
-        <v>5403419</v>
+        <v>2069912</v>
       </c>
       <c r="F128" s="10" t="inlineStr"/>
       <c r="G128" s="10" t="inlineStr"/>
       <c r="H128" s="6" t="n">
-        <v>5403419</v>
+        <v>2069912</v>
       </c>
       <c r="I128" s="11" t="inlineStr"/>
     </row>
@@ -2953,16 +2941,16 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>PMP1269726</t>
+          <t>PMP1269727</t>
         </is>
       </c>
       <c r="E129" s="6" t="n">
-        <v>2069912</v>
+        <v>1332480</v>
       </c>
       <c r="F129" s="10" t="inlineStr"/>
       <c r="G129" s="10" t="inlineStr"/>
       <c r="H129" s="6" t="n">
-        <v>2069912</v>
+        <v>1332480</v>
       </c>
       <c r="I129" s="11" t="inlineStr"/>
     </row>
@@ -2974,16 +2962,16 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>PMP1269727</t>
+          <t>PMP1269738</t>
         </is>
       </c>
       <c r="E130" s="6" t="n">
-        <v>1332480</v>
+        <v>2096654</v>
       </c>
       <c r="F130" s="10" t="inlineStr"/>
       <c r="G130" s="10" t="inlineStr"/>
       <c r="H130" s="6" t="n">
-        <v>1332480</v>
+        <v>2096654</v>
       </c>
       <c r="I130" s="11" t="inlineStr"/>
     </row>
@@ -2995,16 +2983,16 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>PMP1269738</t>
+          <t>PMP1269739</t>
         </is>
       </c>
       <c r="E131" s="6" t="n">
-        <v>2096654</v>
+        <v>61740821</v>
       </c>
       <c r="F131" s="10" t="inlineStr"/>
       <c r="G131" s="10" t="inlineStr"/>
       <c r="H131" s="6" t="n">
-        <v>2096654</v>
+        <v>61740821</v>
       </c>
       <c r="I131" s="11" t="inlineStr"/>
     </row>
@@ -3016,16 +3004,16 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>PMP1269739</t>
+          <t>PMP1269740</t>
         </is>
       </c>
       <c r="E132" s="6" t="n">
-        <v>61740821</v>
+        <v>29463436</v>
       </c>
       <c r="F132" s="10" t="inlineStr"/>
       <c r="G132" s="10" t="inlineStr"/>
       <c r="H132" s="6" t="n">
-        <v>61740821</v>
+        <v>29463436</v>
       </c>
       <c r="I132" s="11" t="inlineStr"/>
     </row>
@@ -3037,16 +3025,16 @@
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>PMP1269740</t>
+          <t>PMP1269742</t>
         </is>
       </c>
       <c r="E133" s="6" t="n">
-        <v>29463436</v>
+        <v>10465349</v>
       </c>
       <c r="F133" s="10" t="inlineStr"/>
       <c r="G133" s="10" t="inlineStr"/>
       <c r="H133" s="6" t="n">
-        <v>29463436</v>
+        <v>10465349</v>
       </c>
       <c r="I133" s="11" t="inlineStr"/>
     </row>
@@ -3058,16 +3046,16 @@
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>PMP1269742</t>
+          <t>PMP1269786</t>
         </is>
       </c>
       <c r="E134" s="6" t="n">
-        <v>10465349</v>
+        <v>1064491</v>
       </c>
       <c r="F134" s="10" t="inlineStr"/>
       <c r="G134" s="10" t="inlineStr"/>
       <c r="H134" s="6" t="n">
-        <v>10465349</v>
+        <v>1064491</v>
       </c>
       <c r="I134" s="11" t="inlineStr"/>
     </row>
@@ -3079,16 +3067,16 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>PMP1269786</t>
+          <t>PMP1269787</t>
         </is>
       </c>
       <c r="E135" s="6" t="n">
-        <v>1064491</v>
+        <v>1952402</v>
       </c>
       <c r="F135" s="10" t="inlineStr"/>
       <c r="G135" s="10" t="inlineStr"/>
       <c r="H135" s="6" t="n">
-        <v>1064491</v>
+        <v>1952402</v>
       </c>
       <c r="I135" s="11" t="inlineStr"/>
     </row>
@@ -3100,16 +3088,16 @@
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>PMP1269787</t>
+          <t>PMP1269976</t>
         </is>
       </c>
       <c r="E136" s="6" t="n">
-        <v>1952402</v>
+        <v>1802549</v>
       </c>
       <c r="F136" s="10" t="inlineStr"/>
       <c r="G136" s="10" t="inlineStr"/>
       <c r="H136" s="6" t="n">
-        <v>1952402</v>
+        <v>1802549</v>
       </c>
       <c r="I136" s="11" t="inlineStr"/>
     </row>
@@ -3121,16 +3109,16 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>PMP1269976</t>
+          <t>PMP1269977</t>
         </is>
       </c>
       <c r="E137" s="6" t="n">
-        <v>1802549</v>
+        <v>461265</v>
       </c>
       <c r="F137" s="10" t="inlineStr"/>
       <c r="G137" s="10" t="inlineStr"/>
       <c r="H137" s="6" t="n">
-        <v>1802549</v>
+        <v>461265</v>
       </c>
       <c r="I137" s="11" t="inlineStr"/>
     </row>
@@ -3142,16 +3130,16 @@
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>PMP1269977</t>
+          <t>PMP1269979</t>
         </is>
       </c>
       <c r="E138" s="6" t="n">
-        <v>461265</v>
+        <v>1608733</v>
       </c>
       <c r="F138" s="10" t="inlineStr"/>
       <c r="G138" s="10" t="inlineStr"/>
       <c r="H138" s="6" t="n">
-        <v>461265</v>
+        <v>1608733</v>
       </c>
       <c r="I138" s="11" t="inlineStr"/>
     </row>
@@ -3163,16 +3151,16 @@
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>PMP1269979</t>
+          <t>PMP1269980</t>
         </is>
       </c>
       <c r="E139" s="6" t="n">
-        <v>1608733</v>
+        <v>369121</v>
       </c>
       <c r="F139" s="10" t="inlineStr"/>
       <c r="G139" s="10" t="inlineStr"/>
       <c r="H139" s="6" t="n">
-        <v>1608733</v>
+        <v>369121</v>
       </c>
       <c r="I139" s="11" t="inlineStr"/>
     </row>
@@ -3184,16 +3172,16 @@
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>PMP1269980</t>
+          <t>PMP1269993</t>
         </is>
       </c>
       <c r="E140" s="6" t="n">
-        <v>369121</v>
+        <v>7444644</v>
       </c>
       <c r="F140" s="10" t="inlineStr"/>
       <c r="G140" s="10" t="inlineStr"/>
       <c r="H140" s="6" t="n">
-        <v>369121</v>
+        <v>7444644</v>
       </c>
       <c r="I140" s="11" t="inlineStr"/>
     </row>
@@ -3205,16 +3193,16 @@
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>PMP1269993</t>
+          <t>PMP1269994</t>
         </is>
       </c>
       <c r="E141" s="6" t="n">
-        <v>7444644</v>
+        <v>1661574</v>
       </c>
       <c r="F141" s="10" t="inlineStr"/>
       <c r="G141" s="10" t="inlineStr"/>
       <c r="H141" s="6" t="n">
-        <v>7444644</v>
+        <v>1661574</v>
       </c>
       <c r="I141" s="11" t="inlineStr"/>
     </row>
@@ -3226,16 +3214,16 @@
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>PMP1269994</t>
+          <t>PMP1269995</t>
         </is>
       </c>
       <c r="E142" s="6" t="n">
-        <v>1661574</v>
+        <v>20971516</v>
       </c>
       <c r="F142" s="10" t="inlineStr"/>
       <c r="G142" s="10" t="inlineStr"/>
       <c r="H142" s="6" t="n">
-        <v>1661574</v>
+        <v>20971516</v>
       </c>
       <c r="I142" s="11" t="inlineStr"/>
     </row>
@@ -3247,16 +3235,16 @@
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>PMP1269995</t>
+          <t>PMP1269996</t>
         </is>
       </c>
       <c r="E143" s="6" t="n">
-        <v>20971516</v>
+        <v>5488395</v>
       </c>
       <c r="F143" s="10" t="inlineStr"/>
       <c r="G143" s="10" t="inlineStr"/>
       <c r="H143" s="6" t="n">
-        <v>20971516</v>
+        <v>5488395</v>
       </c>
       <c r="I143" s="11" t="inlineStr"/>
     </row>
@@ -3268,16 +3256,16 @@
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>PMP1269996</t>
+          <t>PMP1269997</t>
         </is>
       </c>
       <c r="E144" s="6" t="n">
-        <v>5488395</v>
+        <v>97758325</v>
       </c>
       <c r="F144" s="10" t="inlineStr"/>
       <c r="G144" s="10" t="inlineStr"/>
       <c r="H144" s="6" t="n">
-        <v>5488395</v>
+        <v>97758325</v>
       </c>
       <c r="I144" s="11" t="inlineStr"/>
     </row>
@@ -3289,16 +3277,16 @@
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>PMP1269997</t>
+          <t>PMP1269998</t>
         </is>
       </c>
       <c r="E145" s="6" t="n">
-        <v>97758325</v>
+        <v>1172646</v>
       </c>
       <c r="F145" s="10" t="inlineStr"/>
       <c r="G145" s="10" t="inlineStr"/>
       <c r="H145" s="6" t="n">
-        <v>97758325</v>
+        <v>1172646</v>
       </c>
       <c r="I145" s="11" t="inlineStr"/>
     </row>
@@ -3310,16 +3298,16 @@
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>PMP1269998</t>
+          <t>PMP1269999</t>
         </is>
       </c>
       <c r="E146" s="6" t="n">
-        <v>1172646</v>
+        <v>2426772</v>
       </c>
       <c r="F146" s="10" t="inlineStr"/>
       <c r="G146" s="10" t="inlineStr"/>
       <c r="H146" s="6" t="n">
-        <v>1172646</v>
+        <v>2426772</v>
       </c>
       <c r="I146" s="11" t="inlineStr"/>
     </row>
@@ -3331,16 +3319,16 @@
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>PMP1269999</t>
+          <t>PMP1270000</t>
         </is>
       </c>
       <c r="E147" s="6" t="n">
-        <v>2426772</v>
+        <v>95620835</v>
       </c>
       <c r="F147" s="10" t="inlineStr"/>
       <c r="G147" s="10" t="inlineStr"/>
       <c r="H147" s="6" t="n">
-        <v>2426772</v>
+        <v>95620835</v>
       </c>
       <c r="I147" s="11" t="inlineStr"/>
     </row>
@@ -3352,16 +3340,16 @@
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>PMP1270000</t>
+          <t>PMP1270001</t>
         </is>
       </c>
       <c r="E148" s="6" t="n">
-        <v>95620835</v>
+        <v>8453111</v>
       </c>
       <c r="F148" s="10" t="inlineStr"/>
       <c r="G148" s="10" t="inlineStr"/>
       <c r="H148" s="6" t="n">
-        <v>95620835</v>
+        <v>8453111</v>
       </c>
       <c r="I148" s="11" t="inlineStr"/>
     </row>
@@ -3373,16 +3361,16 @@
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>PMP1270001</t>
+          <t>PMP1270002</t>
         </is>
       </c>
       <c r="E149" s="6" t="n">
-        <v>8453111</v>
+        <v>21806172</v>
       </c>
       <c r="F149" s="10" t="inlineStr"/>
       <c r="G149" s="10" t="inlineStr"/>
       <c r="H149" s="6" t="n">
-        <v>8453111</v>
+        <v>21806172</v>
       </c>
       <c r="I149" s="11" t="inlineStr"/>
     </row>
@@ -3394,16 +3382,16 @@
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>PMP1270002</t>
+          <t>PMP1270003</t>
         </is>
       </c>
       <c r="E150" s="6" t="n">
-        <v>21806172</v>
+        <v>5464885</v>
       </c>
       <c r="F150" s="10" t="inlineStr"/>
       <c r="G150" s="10" t="inlineStr"/>
       <c r="H150" s="6" t="n">
-        <v>21806172</v>
+        <v>5464885</v>
       </c>
       <c r="I150" s="11" t="inlineStr"/>
     </row>
@@ -3415,16 +3403,16 @@
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>PMP1270003</t>
+          <t>PMP1270004</t>
         </is>
       </c>
       <c r="E151" s="6" t="n">
-        <v>5464885</v>
+        <v>8197327</v>
       </c>
       <c r="F151" s="10" t="inlineStr"/>
       <c r="G151" s="10" t="inlineStr"/>
       <c r="H151" s="6" t="n">
-        <v>5464885</v>
+        <v>8197327</v>
       </c>
       <c r="I151" s="11" t="inlineStr"/>
     </row>
@@ -3436,16 +3424,16 @@
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>PMP1270004</t>
+          <t>PMP1270005</t>
         </is>
       </c>
       <c r="E152" s="6" t="n">
-        <v>8197327</v>
+        <v>907008</v>
       </c>
       <c r="F152" s="10" t="inlineStr"/>
       <c r="G152" s="10" t="inlineStr"/>
       <c r="H152" s="6" t="n">
-        <v>8197327</v>
+        <v>907008</v>
       </c>
       <c r="I152" s="11" t="inlineStr"/>
     </row>
@@ -3457,16 +3445,16 @@
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>PMP1270005</t>
+          <t>PMP1270057</t>
         </is>
       </c>
       <c r="E153" s="6" t="n">
-        <v>907008</v>
+        <v>66654987</v>
       </c>
       <c r="F153" s="10" t="inlineStr"/>
       <c r="G153" s="10" t="inlineStr"/>
       <c r="H153" s="6" t="n">
-        <v>907008</v>
+        <v>66654987</v>
       </c>
       <c r="I153" s="11" t="inlineStr"/>
     </row>
@@ -3478,16 +3466,16 @@
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>PMP1270057</t>
+          <t>PMP1270058</t>
         </is>
       </c>
       <c r="E154" s="6" t="n">
-        <v>66654987</v>
+        <v>89830321</v>
       </c>
       <c r="F154" s="10" t="inlineStr"/>
       <c r="G154" s="10" t="inlineStr"/>
       <c r="H154" s="6" t="n">
-        <v>66654987</v>
+        <v>89830321</v>
       </c>
       <c r="I154" s="11" t="inlineStr"/>
     </row>
@@ -3499,16 +3487,16 @@
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>PMP1270058</t>
+          <t>PMP1270059</t>
         </is>
       </c>
       <c r="E155" s="6" t="n">
-        <v>89830321</v>
+        <v>155858658</v>
       </c>
       <c r="F155" s="10" t="inlineStr"/>
       <c r="G155" s="10" t="inlineStr"/>
       <c r="H155" s="6" t="n">
-        <v>89830321</v>
+        <v>155858658</v>
       </c>
       <c r="I155" s="11" t="inlineStr"/>
     </row>
@@ -3520,16 +3508,16 @@
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>PMP1270059</t>
+          <t>PMP1270060</t>
         </is>
       </c>
       <c r="E156" s="6" t="n">
-        <v>155858658</v>
+        <v>1835785</v>
       </c>
       <c r="F156" s="10" t="inlineStr"/>
       <c r="G156" s="10" t="inlineStr"/>
       <c r="H156" s="6" t="n">
-        <v>155858658</v>
+        <v>1835785</v>
       </c>
       <c r="I156" s="11" t="inlineStr"/>
     </row>
@@ -3541,16 +3529,16 @@
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>PMP1270060</t>
+          <t>PMP1270061</t>
         </is>
       </c>
       <c r="E157" s="6" t="n">
-        <v>1835785</v>
+        <v>1548384</v>
       </c>
       <c r="F157" s="10" t="inlineStr"/>
       <c r="G157" s="10" t="inlineStr"/>
       <c r="H157" s="6" t="n">
-        <v>1835785</v>
+        <v>1548384</v>
       </c>
       <c r="I157" s="11" t="inlineStr"/>
     </row>
@@ -3562,16 +3550,16 @@
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>PMP1270061</t>
+          <t>PMP1270062</t>
         </is>
       </c>
       <c r="E158" s="6" t="n">
-        <v>1548384</v>
+        <v>2579996</v>
       </c>
       <c r="F158" s="10" t="inlineStr"/>
       <c r="G158" s="10" t="inlineStr"/>
       <c r="H158" s="6" t="n">
-        <v>1548384</v>
+        <v>2579996</v>
       </c>
       <c r="I158" s="11" t="inlineStr"/>
     </row>
@@ -3583,16 +3571,16 @@
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>PMP1270062</t>
+          <t>PMP1270063</t>
         </is>
       </c>
       <c r="E159" s="6" t="n">
-        <v>2579996</v>
+        <v>2732442</v>
       </c>
       <c r="F159" s="10" t="inlineStr"/>
       <c r="G159" s="10" t="inlineStr"/>
       <c r="H159" s="6" t="n">
-        <v>2579996</v>
+        <v>2732442</v>
       </c>
       <c r="I159" s="11" t="inlineStr"/>
     </row>
@@ -3604,16 +3592,16 @@
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>PMP1270063</t>
+          <t>PMP1270066</t>
         </is>
       </c>
       <c r="E160" s="6" t="n">
-        <v>2732442</v>
+        <v>2587041</v>
       </c>
       <c r="F160" s="10" t="inlineStr"/>
       <c r="G160" s="10" t="inlineStr"/>
       <c r="H160" s="6" t="n">
-        <v>2732442</v>
+        <v>2587041</v>
       </c>
       <c r="I160" s="11" t="inlineStr"/>
     </row>
@@ -3625,16 +3613,16 @@
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>PMP1270066</t>
+          <t>PMP1270067</t>
         </is>
       </c>
       <c r="E161" s="6" t="n">
-        <v>2587041</v>
+        <v>1153447</v>
       </c>
       <c r="F161" s="10" t="inlineStr"/>
       <c r="G161" s="10" t="inlineStr"/>
       <c r="H161" s="6" t="n">
-        <v>2587041</v>
+        <v>1153447</v>
       </c>
       <c r="I161" s="11" t="inlineStr"/>
     </row>
@@ -3646,16 +3634,16 @@
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>PMP1270067</t>
+          <t>PMP1270068</t>
         </is>
       </c>
       <c r="E162" s="6" t="n">
-        <v>1153447</v>
+        <v>4598710</v>
       </c>
       <c r="F162" s="10" t="inlineStr"/>
       <c r="G162" s="10" t="inlineStr"/>
       <c r="H162" s="6" t="n">
-        <v>1153447</v>
+        <v>4598710</v>
       </c>
       <c r="I162" s="11" t="inlineStr"/>
     </row>
@@ -3667,16 +3655,16 @@
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>PMP1270068</t>
+          <t>PMP1270069</t>
         </is>
       </c>
       <c r="E163" s="6" t="n">
-        <v>4598710</v>
+        <v>15046014</v>
       </c>
       <c r="F163" s="10" t="inlineStr"/>
       <c r="G163" s="10" t="inlineStr"/>
       <c r="H163" s="6" t="n">
-        <v>4598710</v>
+        <v>15046014</v>
       </c>
       <c r="I163" s="11" t="inlineStr"/>
     </row>
@@ -3688,16 +3676,16 @@
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>PMP1270069</t>
+          <t>PMP1270070</t>
         </is>
       </c>
       <c r="E164" s="6" t="n">
-        <v>15046014</v>
+        <v>131087523</v>
       </c>
       <c r="F164" s="10" t="inlineStr"/>
       <c r="G164" s="10" t="inlineStr"/>
       <c r="H164" s="6" t="n">
-        <v>15046014</v>
+        <v>131087523</v>
       </c>
       <c r="I164" s="11" t="inlineStr"/>
     </row>
@@ -3709,16 +3697,16 @@
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>PMP1270070</t>
+          <t>PMP1270071</t>
         </is>
       </c>
       <c r="E165" s="6" t="n">
-        <v>131087523</v>
+        <v>2826240</v>
       </c>
       <c r="F165" s="10" t="inlineStr"/>
       <c r="G165" s="10" t="inlineStr"/>
       <c r="H165" s="6" t="n">
-        <v>131087523</v>
+        <v>2826240</v>
       </c>
       <c r="I165" s="11" t="inlineStr"/>
     </row>
@@ -3730,16 +3718,16 @@
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>PMP1270071</t>
+          <t>PMP1270072</t>
         </is>
       </c>
       <c r="E166" s="6" t="n">
-        <v>2826240</v>
+        <v>52040683</v>
       </c>
       <c r="F166" s="10" t="inlineStr"/>
       <c r="G166" s="10" t="inlineStr"/>
       <c r="H166" s="6" t="n">
-        <v>2826240</v>
+        <v>52040683</v>
       </c>
       <c r="I166" s="11" t="inlineStr"/>
     </row>
@@ -3751,16 +3739,16 @@
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>PMP1270072</t>
+          <t>PMP1270073</t>
         </is>
       </c>
       <c r="E167" s="6" t="n">
-        <v>52040683</v>
+        <v>636600</v>
       </c>
       <c r="F167" s="10" t="inlineStr"/>
       <c r="G167" s="10" t="inlineStr"/>
       <c r="H167" s="6" t="n">
-        <v>52040683</v>
+        <v>636600</v>
       </c>
       <c r="I167" s="11" t="inlineStr"/>
     </row>
@@ -3772,16 +3760,16 @@
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>PMP1270073</t>
+          <t>PMP1270074</t>
         </is>
       </c>
       <c r="E168" s="6" t="n">
-        <v>636600</v>
+        <v>1818846</v>
       </c>
       <c r="F168" s="10" t="inlineStr"/>
       <c r="G168" s="10" t="inlineStr"/>
       <c r="H168" s="6" t="n">
-        <v>636600</v>
+        <v>1818846</v>
       </c>
       <c r="I168" s="11" t="inlineStr"/>
     </row>
@@ -3793,16 +3781,16 @@
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>PMP1270074</t>
+          <t>PMP1270075</t>
         </is>
       </c>
       <c r="E169" s="6" t="n">
-        <v>1818846</v>
+        <v>93184558</v>
       </c>
       <c r="F169" s="10" t="inlineStr"/>
       <c r="G169" s="10" t="inlineStr"/>
       <c r="H169" s="6" t="n">
-        <v>1818846</v>
+        <v>93184558</v>
       </c>
       <c r="I169" s="11" t="inlineStr"/>
     </row>
@@ -3814,16 +3802,16 @@
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>PMP1270075</t>
+          <t>PMP1270076</t>
         </is>
       </c>
       <c r="E170" s="6" t="n">
-        <v>93184558</v>
+        <v>79280015</v>
       </c>
       <c r="F170" s="10" t="inlineStr"/>
       <c r="G170" s="10" t="inlineStr"/>
       <c r="H170" s="6" t="n">
-        <v>93184558</v>
+        <v>79280015</v>
       </c>
       <c r="I170" s="11" t="inlineStr"/>
     </row>
@@ -3835,16 +3823,16 @@
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>PMP1270076</t>
+          <t>PMP1270077</t>
         </is>
       </c>
       <c r="E171" s="6" t="n">
-        <v>79280015</v>
+        <v>124458003</v>
       </c>
       <c r="F171" s="10" t="inlineStr"/>
       <c r="G171" s="10" t="inlineStr"/>
       <c r="H171" s="6" t="n">
-        <v>79280015</v>
+        <v>124458003</v>
       </c>
       <c r="I171" s="11" t="inlineStr"/>
     </row>
@@ -3856,16 +3844,16 @@
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>PMP1270077</t>
+          <t>PMP1270078</t>
         </is>
       </c>
       <c r="E172" s="6" t="n">
-        <v>124458003</v>
+        <v>3624011</v>
       </c>
       <c r="F172" s="10" t="inlineStr"/>
       <c r="G172" s="10" t="inlineStr"/>
       <c r="H172" s="6" t="n">
-        <v>124458003</v>
+        <v>3624011</v>
       </c>
       <c r="I172" s="11" t="inlineStr"/>
     </row>
@@ -3877,16 +3865,16 @@
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>PMP1270078</t>
+          <t>PMP1270079</t>
         </is>
       </c>
       <c r="E173" s="6" t="n">
-        <v>3624011</v>
+        <v>111179948</v>
       </c>
       <c r="F173" s="10" t="inlineStr"/>
       <c r="G173" s="10" t="inlineStr"/>
       <c r="H173" s="6" t="n">
-        <v>3624011</v>
+        <v>111179948</v>
       </c>
       <c r="I173" s="11" t="inlineStr"/>
     </row>
@@ -3898,16 +3886,16 @@
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>PMP1270079</t>
+          <t>PMP1270080</t>
         </is>
       </c>
       <c r="E174" s="6" t="n">
-        <v>111179948</v>
+        <v>4772712</v>
       </c>
       <c r="F174" s="10" t="inlineStr"/>
       <c r="G174" s="10" t="inlineStr"/>
       <c r="H174" s="6" t="n">
-        <v>111179948</v>
+        <v>4772712</v>
       </c>
       <c r="I174" s="11" t="inlineStr"/>
     </row>
@@ -3919,16 +3907,16 @@
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>PMP1270080</t>
+          <t>PMP1270081</t>
         </is>
       </c>
       <c r="E175" s="6" t="n">
-        <v>4772712</v>
+        <v>53114517</v>
       </c>
       <c r="F175" s="10" t="inlineStr"/>
       <c r="G175" s="10" t="inlineStr"/>
       <c r="H175" s="6" t="n">
-        <v>4772712</v>
+        <v>53114517</v>
       </c>
       <c r="I175" s="11" t="inlineStr"/>
     </row>
@@ -3940,16 +3928,16 @@
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>PMP1270081</t>
+          <t>PMP1270082</t>
         </is>
       </c>
       <c r="E176" s="6" t="n">
-        <v>53114517</v>
+        <v>43168085</v>
       </c>
       <c r="F176" s="10" t="inlineStr"/>
       <c r="G176" s="10" t="inlineStr"/>
       <c r="H176" s="6" t="n">
-        <v>53114517</v>
+        <v>43168085</v>
       </c>
       <c r="I176" s="11" t="inlineStr"/>
     </row>
@@ -3961,16 +3949,16 @@
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>PMP1270082</t>
+          <t>PMP1270083</t>
         </is>
       </c>
       <c r="E177" s="6" t="n">
-        <v>43168085</v>
+        <v>4255528</v>
       </c>
       <c r="F177" s="10" t="inlineStr"/>
       <c r="G177" s="10" t="inlineStr"/>
       <c r="H177" s="6" t="n">
-        <v>43168085</v>
+        <v>4255528</v>
       </c>
       <c r="I177" s="11" t="inlineStr"/>
     </row>
@@ -3982,16 +3970,16 @@
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>PMP1270083</t>
+          <t>PMP1270084</t>
         </is>
       </c>
       <c r="E178" s="6" t="n">
-        <v>4255528</v>
+        <v>8019548</v>
       </c>
       <c r="F178" s="10" t="inlineStr"/>
       <c r="G178" s="10" t="inlineStr"/>
       <c r="H178" s="6" t="n">
-        <v>4255528</v>
+        <v>8019548</v>
       </c>
       <c r="I178" s="11" t="inlineStr"/>
     </row>
@@ -4003,16 +3991,16 @@
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>PMP1270084</t>
+          <t>PMP1270085</t>
         </is>
       </c>
       <c r="E179" s="6" t="n">
-        <v>8019548</v>
+        <v>1062097</v>
       </c>
       <c r="F179" s="10" t="inlineStr"/>
       <c r="G179" s="10" t="inlineStr"/>
       <c r="H179" s="6" t="n">
-        <v>8019548</v>
+        <v>1062097</v>
       </c>
       <c r="I179" s="11" t="inlineStr"/>
     </row>
@@ -4024,16 +4012,16 @@
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>PMP1270085</t>
+          <t>PMP1270086</t>
         </is>
       </c>
       <c r="E180" s="6" t="n">
-        <v>1062097</v>
+        <v>6911713</v>
       </c>
       <c r="F180" s="10" t="inlineStr"/>
       <c r="G180" s="10" t="inlineStr"/>
       <c r="H180" s="6" t="n">
-        <v>1062097</v>
+        <v>6911713</v>
       </c>
       <c r="I180" s="11" t="inlineStr"/>
     </row>
@@ -4045,16 +4033,16 @@
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>PMP1270086</t>
+          <t>PMP1270087</t>
         </is>
       </c>
       <c r="E181" s="6" t="n">
-        <v>6911713</v>
+        <v>3459583</v>
       </c>
       <c r="F181" s="10" t="inlineStr"/>
       <c r="G181" s="10" t="inlineStr"/>
       <c r="H181" s="6" t="n">
-        <v>6911713</v>
+        <v>3459583</v>
       </c>
       <c r="I181" s="11" t="inlineStr"/>
     </row>
@@ -4066,16 +4054,16 @@
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>PMP1270087</t>
+          <t>PMP1270088</t>
         </is>
       </c>
       <c r="E182" s="6" t="n">
-        <v>3459583</v>
+        <v>5100194</v>
       </c>
       <c r="F182" s="10" t="inlineStr"/>
       <c r="G182" s="10" t="inlineStr"/>
       <c r="H182" s="6" t="n">
-        <v>3459583</v>
+        <v>5100194</v>
       </c>
       <c r="I182" s="11" t="inlineStr"/>
     </row>
@@ -4087,16 +4075,16 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>PMP1270088</t>
+          <t>PMP1270089</t>
         </is>
       </c>
       <c r="E183" s="6" t="n">
-        <v>5100194</v>
+        <v>44010753</v>
       </c>
       <c r="F183" s="10" t="inlineStr"/>
       <c r="G183" s="10" t="inlineStr"/>
       <c r="H183" s="6" t="n">
-        <v>5100194</v>
+        <v>44010753</v>
       </c>
       <c r="I183" s="11" t="inlineStr"/>
     </row>
@@ -4108,16 +4096,16 @@
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>PMP1270089</t>
+          <t>PMP1270090</t>
         </is>
       </c>
       <c r="E184" s="6" t="n">
-        <v>44010753</v>
+        <v>6974550</v>
       </c>
       <c r="F184" s="10" t="inlineStr"/>
       <c r="G184" s="10" t="inlineStr"/>
       <c r="H184" s="6" t="n">
-        <v>44010753</v>
+        <v>6974550</v>
       </c>
       <c r="I184" s="11" t="inlineStr"/>
     </row>
@@ -4129,16 +4117,16 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>PMP1270090</t>
+          <t>PMP1270091</t>
         </is>
       </c>
       <c r="E185" s="6" t="n">
-        <v>6974550</v>
+        <v>31112253</v>
       </c>
       <c r="F185" s="10" t="inlineStr"/>
       <c r="G185" s="10" t="inlineStr"/>
       <c r="H185" s="6" t="n">
-        <v>6974550</v>
+        <v>31112253</v>
       </c>
       <c r="I185" s="11" t="inlineStr"/>
     </row>
@@ -4150,16 +4138,16 @@
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>PMP1270091</t>
+          <t>PMP1270092</t>
         </is>
       </c>
       <c r="E186" s="6" t="n">
-        <v>31112253</v>
+        <v>14153160</v>
       </c>
       <c r="F186" s="10" t="inlineStr"/>
       <c r="G186" s="10" t="inlineStr"/>
       <c r="H186" s="6" t="n">
-        <v>31112253</v>
+        <v>14153160</v>
       </c>
       <c r="I186" s="11" t="inlineStr"/>
     </row>
@@ -4171,16 +4159,16 @@
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>PMP1270092</t>
+          <t>PMP1270093</t>
         </is>
       </c>
       <c r="E187" s="6" t="n">
-        <v>14153160</v>
+        <v>38365287</v>
       </c>
       <c r="F187" s="10" t="inlineStr"/>
       <c r="G187" s="10" t="inlineStr"/>
       <c r="H187" s="6" t="n">
-        <v>14153160</v>
+        <v>38365287</v>
       </c>
       <c r="I187" s="11" t="inlineStr"/>
     </row>
@@ -4192,16 +4180,16 @@
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>PMP1270093</t>
+          <t>PMP1270094</t>
         </is>
       </c>
       <c r="E188" s="6" t="n">
-        <v>38365287</v>
+        <v>4010252</v>
       </c>
       <c r="F188" s="10" t="inlineStr"/>
       <c r="G188" s="10" t="inlineStr"/>
       <c r="H188" s="6" t="n">
-        <v>38365287</v>
+        <v>4010252</v>
       </c>
       <c r="I188" s="11" t="inlineStr"/>
     </row>
@@ -4213,16 +4201,16 @@
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>PMP1270094</t>
+          <t>PMP1270095</t>
         </is>
       </c>
       <c r="E189" s="6" t="n">
-        <v>4010252</v>
+        <v>429999</v>
       </c>
       <c r="F189" s="10" t="inlineStr"/>
       <c r="G189" s="10" t="inlineStr"/>
       <c r="H189" s="6" t="n">
-        <v>4010252</v>
+        <v>429999</v>
       </c>
       <c r="I189" s="11" t="inlineStr"/>
     </row>
@@ -4234,16 +4222,16 @@
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>PMP1270095</t>
+          <t>PMP1270096</t>
         </is>
       </c>
       <c r="E190" s="6" t="n">
-        <v>429999</v>
+        <v>546488</v>
       </c>
       <c r="F190" s="10" t="inlineStr"/>
       <c r="G190" s="10" t="inlineStr"/>
       <c r="H190" s="6" t="n">
-        <v>429999</v>
+        <v>546488</v>
       </c>
       <c r="I190" s="11" t="inlineStr"/>
     </row>
@@ -4255,16 +4243,16 @@
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>PMP1270096</t>
+          <t>PMP1270294</t>
         </is>
       </c>
       <c r="E191" s="6" t="n">
-        <v>546488</v>
+        <v>42622893</v>
       </c>
       <c r="F191" s="10" t="inlineStr"/>
       <c r="G191" s="10" t="inlineStr"/>
       <c r="H191" s="6" t="n">
-        <v>546488</v>
+        <v>42622893</v>
       </c>
       <c r="I191" s="11" t="inlineStr"/>
     </row>
@@ -4276,16 +4264,16 @@
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>PMP1270294</t>
+          <t>PMP1270296</t>
         </is>
       </c>
       <c r="E192" s="6" t="n">
-        <v>42622893</v>
+        <v>5647047</v>
       </c>
       <c r="F192" s="10" t="inlineStr"/>
       <c r="G192" s="10" t="inlineStr"/>
       <c r="H192" s="6" t="n">
-        <v>42622893</v>
+        <v>5647047</v>
       </c>
       <c r="I192" s="11" t="inlineStr"/>
     </row>
@@ -4297,16 +4285,16 @@
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>PMP1270296</t>
+          <t>PMP1270297</t>
         </is>
       </c>
       <c r="E193" s="6" t="n">
-        <v>5647047</v>
+        <v>1580215</v>
       </c>
       <c r="F193" s="10" t="inlineStr"/>
       <c r="G193" s="10" t="inlineStr"/>
       <c r="H193" s="6" t="n">
-        <v>5647047</v>
+        <v>1580215</v>
       </c>
       <c r="I193" s="11" t="inlineStr"/>
     </row>
@@ -4318,16 +4306,16 @@
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>PMP1270297</t>
+          <t>PMP1270298</t>
         </is>
       </c>
       <c r="E194" s="6" t="n">
-        <v>1580215</v>
+        <v>273244</v>
       </c>
       <c r="F194" s="10" t="inlineStr"/>
       <c r="G194" s="10" t="inlineStr"/>
       <c r="H194" s="6" t="n">
-        <v>1580215</v>
+        <v>273244</v>
       </c>
       <c r="I194" s="11" t="inlineStr"/>
     </row>
@@ -4339,16 +4327,16 @@
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>PMP1270298</t>
+          <t>PMP1270315</t>
         </is>
       </c>
       <c r="E195" s="6" t="n">
-        <v>273244</v>
+        <v>1648390</v>
       </c>
       <c r="F195" s="10" t="inlineStr"/>
       <c r="G195" s="10" t="inlineStr"/>
       <c r="H195" s="6" t="n">
-        <v>273244</v>
+        <v>1648390</v>
       </c>
       <c r="I195" s="11" t="inlineStr"/>
     </row>
@@ -4360,16 +4348,16 @@
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>PMP1270315</t>
+          <t>PMP1270316</t>
         </is>
       </c>
       <c r="E196" s="6" t="n">
-        <v>1648390</v>
+        <v>260059645</v>
       </c>
       <c r="F196" s="10" t="inlineStr"/>
       <c r="G196" s="10" t="inlineStr"/>
       <c r="H196" s="6" t="n">
-        <v>1648390</v>
+        <v>260059645</v>
       </c>
       <c r="I196" s="11" t="inlineStr"/>
     </row>
@@ -4381,16 +4369,16 @@
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>PMP1270316</t>
+          <t>PMP1270317</t>
         </is>
       </c>
       <c r="E197" s="6" t="n">
-        <v>260059645</v>
+        <v>13775821</v>
       </c>
       <c r="F197" s="10" t="inlineStr"/>
       <c r="G197" s="10" t="inlineStr"/>
       <c r="H197" s="6" t="n">
-        <v>260059645</v>
+        <v>13775821</v>
       </c>
       <c r="I197" s="11" t="inlineStr"/>
     </row>
@@ -4402,16 +4390,16 @@
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>PMP1270317</t>
+          <t>PMP1270318</t>
         </is>
       </c>
       <c r="E198" s="6" t="n">
-        <v>13775821</v>
+        <v>16239655</v>
       </c>
       <c r="F198" s="10" t="inlineStr"/>
       <c r="G198" s="10" t="inlineStr"/>
       <c r="H198" s="6" t="n">
-        <v>13775821</v>
+        <v>16239655</v>
       </c>
       <c r="I198" s="11" t="inlineStr"/>
     </row>
@@ -4423,16 +4411,16 @@
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>PMP1270318</t>
+          <t>PMP1270319</t>
         </is>
       </c>
       <c r="E199" s="6" t="n">
-        <v>16239655</v>
+        <v>4404721</v>
       </c>
       <c r="F199" s="10" t="inlineStr"/>
       <c r="G199" s="10" t="inlineStr"/>
       <c r="H199" s="6" t="n">
-        <v>16239655</v>
+        <v>4404721</v>
       </c>
       <c r="I199" s="11" t="inlineStr"/>
     </row>
@@ -4444,16 +4432,16 @@
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>PMP1270319</t>
+          <t>PMP1270320</t>
         </is>
       </c>
       <c r="E200" s="6" t="n">
-        <v>4404721</v>
+        <v>1420321</v>
       </c>
       <c r="F200" s="10" t="inlineStr"/>
       <c r="G200" s="10" t="inlineStr"/>
       <c r="H200" s="6" t="n">
-        <v>4404721</v>
+        <v>1420321</v>
       </c>
       <c r="I200" s="11" t="inlineStr"/>
     </row>
@@ -4465,16 +4453,16 @@
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>PMP1270320</t>
+          <t>PMP1270321</t>
         </is>
       </c>
       <c r="E201" s="6" t="n">
-        <v>1420321</v>
+        <v>210519194</v>
       </c>
       <c r="F201" s="10" t="inlineStr"/>
       <c r="G201" s="10" t="inlineStr"/>
       <c r="H201" s="6" t="n">
-        <v>1420321</v>
+        <v>210519194</v>
       </c>
       <c r="I201" s="11" t="inlineStr"/>
     </row>
@@ -4486,16 +4474,16 @@
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>PMP1270321</t>
+          <t>PMP1270335</t>
         </is>
       </c>
       <c r="E202" s="6" t="n">
-        <v>210519194</v>
+        <v>2798799</v>
       </c>
       <c r="F202" s="10" t="inlineStr"/>
       <c r="G202" s="10" t="inlineStr"/>
       <c r="H202" s="6" t="n">
-        <v>210519194</v>
+        <v>2798799</v>
       </c>
       <c r="I202" s="11" t="inlineStr"/>
     </row>
@@ -4507,16 +4495,16 @@
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>PMP1270335</t>
+          <t>PMP1270336</t>
         </is>
       </c>
       <c r="E203" s="6" t="n">
-        <v>2798799</v>
+        <v>1115075</v>
       </c>
       <c r="F203" s="10" t="inlineStr"/>
       <c r="G203" s="10" t="inlineStr"/>
       <c r="H203" s="6" t="n">
-        <v>2798799</v>
+        <v>1115075</v>
       </c>
       <c r="I203" s="11" t="inlineStr"/>
     </row>
@@ -4528,16 +4516,16 @@
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>PMP1270336</t>
+          <t>PMP1270337</t>
         </is>
       </c>
       <c r="E204" s="6" t="n">
-        <v>1115075</v>
+        <v>8504497</v>
       </c>
       <c r="F204" s="10" t="inlineStr"/>
       <c r="G204" s="10" t="inlineStr"/>
       <c r="H204" s="6" t="n">
-        <v>1115075</v>
+        <v>8504497</v>
       </c>
       <c r="I204" s="11" t="inlineStr"/>
     </row>
@@ -4549,16 +4537,16 @@
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>PMP1270337</t>
+          <t>PMP1270338</t>
         </is>
       </c>
       <c r="E205" s="6" t="n">
-        <v>8504497</v>
+        <v>1382118</v>
       </c>
       <c r="F205" s="10" t="inlineStr"/>
       <c r="G205" s="10" t="inlineStr"/>
       <c r="H205" s="6" t="n">
-        <v>8504497</v>
+        <v>1382118</v>
       </c>
       <c r="I205" s="11" t="inlineStr"/>
     </row>
@@ -4570,16 +4558,16 @@
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>PMP1270338</t>
+          <t>PMP1270339</t>
         </is>
       </c>
       <c r="E206" s="6" t="n">
-        <v>1382118</v>
+        <v>67156371</v>
       </c>
       <c r="F206" s="10" t="inlineStr"/>
       <c r="G206" s="10" t="inlineStr"/>
       <c r="H206" s="6" t="n">
-        <v>1382118</v>
+        <v>67156371</v>
       </c>
       <c r="I206" s="11" t="inlineStr"/>
     </row>
@@ -4591,16 +4579,16 @@
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>PMP1270339</t>
+          <t>PMP1270340</t>
         </is>
       </c>
       <c r="E207" s="6" t="n">
-        <v>67156371</v>
+        <v>1934997</v>
       </c>
       <c r="F207" s="10" t="inlineStr"/>
       <c r="G207" s="10" t="inlineStr"/>
       <c r="H207" s="6" t="n">
-        <v>67156371</v>
+        <v>1934997</v>
       </c>
       <c r="I207" s="11" t="inlineStr"/>
     </row>
@@ -4612,16 +4600,16 @@
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>PMP1270340</t>
+          <t>PMP1270341</t>
         </is>
       </c>
       <c r="E208" s="6" t="n">
-        <v>1934997</v>
+        <v>364326</v>
       </c>
       <c r="F208" s="10" t="inlineStr"/>
       <c r="G208" s="10" t="inlineStr"/>
       <c r="H208" s="6" t="n">
-        <v>1934997</v>
+        <v>364326</v>
       </c>
       <c r="I208" s="11" t="inlineStr"/>
     </row>
@@ -4633,16 +4621,16 @@
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>PMP1270341</t>
+          <t>PMP1270342</t>
         </is>
       </c>
       <c r="E209" s="6" t="n">
-        <v>364326</v>
+        <v>1275140</v>
       </c>
       <c r="F209" s="10" t="inlineStr"/>
       <c r="G209" s="10" t="inlineStr"/>
       <c r="H209" s="6" t="n">
-        <v>364326</v>
+        <v>1275140</v>
       </c>
       <c r="I209" s="11" t="inlineStr"/>
     </row>
@@ -4654,16 +4642,16 @@
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>PMP1270342</t>
+          <t>PMP1270343</t>
         </is>
       </c>
       <c r="E210" s="6" t="n">
-        <v>1275140</v>
+        <v>6141816</v>
       </c>
       <c r="F210" s="10" t="inlineStr"/>
       <c r="G210" s="10" t="inlineStr"/>
       <c r="H210" s="6" t="n">
-        <v>1275140</v>
+        <v>6141816</v>
       </c>
       <c r="I210" s="11" t="inlineStr"/>
     </row>
@@ -4675,16 +4663,16 @@
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>PMP1270343</t>
+          <t>PMP1270344</t>
         </is>
       </c>
       <c r="E211" s="6" t="n">
-        <v>6141816</v>
+        <v>33576336</v>
       </c>
       <c r="F211" s="10" t="inlineStr"/>
       <c r="G211" s="10" t="inlineStr"/>
       <c r="H211" s="6" t="n">
-        <v>6141816</v>
+        <v>33576336</v>
       </c>
       <c r="I211" s="11" t="inlineStr"/>
     </row>
@@ -4696,16 +4684,16 @@
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>PMP1270344</t>
+          <t>PMP1270345</t>
         </is>
       </c>
       <c r="E212" s="6" t="n">
-        <v>33576336</v>
+        <v>15729160</v>
       </c>
       <c r="F212" s="10" t="inlineStr"/>
       <c r="G212" s="10" t="inlineStr"/>
       <c r="H212" s="6" t="n">
-        <v>33576336</v>
+        <v>15729160</v>
       </c>
       <c r="I212" s="11" t="inlineStr"/>
     </row>
@@ -4717,16 +4705,16 @@
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>PMP1270345</t>
+          <t>PMP1270346</t>
         </is>
       </c>
       <c r="E213" s="6" t="n">
-        <v>15729160</v>
+        <v>40926768</v>
       </c>
       <c r="F213" s="10" t="inlineStr"/>
       <c r="G213" s="10" t="inlineStr"/>
       <c r="H213" s="6" t="n">
-        <v>15729160</v>
+        <v>40926768</v>
       </c>
       <c r="I213" s="11" t="inlineStr"/>
     </row>
@@ -4738,16 +4726,16 @@
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>PMP1270346</t>
+          <t>PMP1270347</t>
         </is>
       </c>
       <c r="E214" s="6" t="n">
-        <v>40926768</v>
+        <v>87542406</v>
       </c>
       <c r="F214" s="10" t="inlineStr"/>
       <c r="G214" s="10" t="inlineStr"/>
       <c r="H214" s="6" t="n">
-        <v>40926768</v>
+        <v>87542406</v>
       </c>
       <c r="I214" s="11" t="inlineStr"/>
     </row>
@@ -4759,16 +4747,16 @@
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>PMP1270347</t>
+          <t>PMP1270348</t>
         </is>
       </c>
       <c r="E215" s="6" t="n">
-        <v>87542406</v>
+        <v>263878477</v>
       </c>
       <c r="F215" s="10" t="inlineStr"/>
       <c r="G215" s="10" t="inlineStr"/>
       <c r="H215" s="6" t="n">
-        <v>87542406</v>
+        <v>263878477</v>
       </c>
       <c r="I215" s="11" t="inlineStr"/>
     </row>
@@ -4780,16 +4768,16 @@
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>PMP1270348</t>
+          <t>PMP1270349</t>
         </is>
       </c>
       <c r="E216" s="6" t="n">
-        <v>263878477</v>
+        <v>7889336</v>
       </c>
       <c r="F216" s="10" t="inlineStr"/>
       <c r="G216" s="10" t="inlineStr"/>
       <c r="H216" s="6" t="n">
-        <v>263878477</v>
+        <v>7889336</v>
       </c>
       <c r="I216" s="11" t="inlineStr"/>
     </row>
@@ -4801,16 +4789,16 @@
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>PMP1270349</t>
+          <t>PMP1270350</t>
         </is>
       </c>
       <c r="E217" s="6" t="n">
-        <v>7889336</v>
+        <v>251066887</v>
       </c>
       <c r="F217" s="10" t="inlineStr"/>
       <c r="G217" s="10" t="inlineStr"/>
       <c r="H217" s="6" t="n">
-        <v>7889336</v>
+        <v>251066887</v>
       </c>
       <c r="I217" s="11" t="inlineStr"/>
     </row>
@@ -4822,16 +4810,16 @@
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>PMP1270350</t>
+          <t>PMP1270351</t>
         </is>
       </c>
       <c r="E218" s="6" t="n">
-        <v>251066887</v>
+        <v>28429180</v>
       </c>
       <c r="F218" s="10" t="inlineStr"/>
       <c r="G218" s="10" t="inlineStr"/>
       <c r="H218" s="6" t="n">
-        <v>251066887</v>
+        <v>28429180</v>
       </c>
       <c r="I218" s="11" t="inlineStr"/>
     </row>
@@ -4843,16 +4831,16 @@
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>PMP1270351</t>
+          <t>PMP1270352</t>
         </is>
       </c>
       <c r="E219" s="6" t="n">
-        <v>28429180</v>
+        <v>924006</v>
       </c>
       <c r="F219" s="10" t="inlineStr"/>
       <c r="G219" s="10" t="inlineStr"/>
       <c r="H219" s="6" t="n">
-        <v>28429180</v>
+        <v>924006</v>
       </c>
       <c r="I219" s="11" t="inlineStr"/>
     </row>
@@ -4864,16 +4852,16 @@
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>PMP1270352</t>
+          <t>PMP1270353</t>
         </is>
       </c>
       <c r="E220" s="6" t="n">
-        <v>924006</v>
+        <v>37861079</v>
       </c>
       <c r="F220" s="10" t="inlineStr"/>
       <c r="G220" s="10" t="inlineStr"/>
       <c r="H220" s="6" t="n">
-        <v>924006</v>
+        <v>37861079</v>
       </c>
       <c r="I220" s="11" t="inlineStr"/>
     </row>
@@ -4885,16 +4873,16 @@
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>PMP1270353</t>
+          <t>PMP1270354</t>
         </is>
       </c>
       <c r="E221" s="6" t="n">
-        <v>37861079</v>
+        <v>30102202</v>
       </c>
       <c r="F221" s="10" t="inlineStr"/>
       <c r="G221" s="10" t="inlineStr"/>
       <c r="H221" s="6" t="n">
-        <v>37861079</v>
+        <v>30102202</v>
       </c>
       <c r="I221" s="11" t="inlineStr"/>
     </row>
@@ -4906,16 +4894,16 @@
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>PMP1270354</t>
+          <t>PMP1270355</t>
         </is>
       </c>
       <c r="E222" s="6" t="n">
-        <v>30102202</v>
+        <v>11006484</v>
       </c>
       <c r="F222" s="10" t="inlineStr"/>
       <c r="G222" s="10" t="inlineStr"/>
       <c r="H222" s="6" t="n">
-        <v>30102202</v>
+        <v>11006484</v>
       </c>
       <c r="I222" s="11" t="inlineStr"/>
     </row>
@@ -4927,16 +4915,16 @@
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>PMP1270355</t>
+          <t>PMP1270484</t>
         </is>
       </c>
       <c r="E223" s="6" t="n">
-        <v>11006484</v>
+        <v>12228884</v>
       </c>
       <c r="F223" s="10" t="inlineStr"/>
       <c r="G223" s="10" t="inlineStr"/>
       <c r="H223" s="6" t="n">
-        <v>11006484</v>
+        <v>12228884</v>
       </c>
       <c r="I223" s="11" t="inlineStr"/>
     </row>
@@ -4948,16 +4936,16 @@
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>PMP1270484</t>
+          <t>PMP1270485</t>
         </is>
       </c>
       <c r="E224" s="6" t="n">
-        <v>12228884</v>
+        <v>24112073</v>
       </c>
       <c r="F224" s="10" t="inlineStr"/>
       <c r="G224" s="10" t="inlineStr"/>
       <c r="H224" s="6" t="n">
-        <v>12228884</v>
+        <v>24112073</v>
       </c>
       <c r="I224" s="11" t="inlineStr"/>
     </row>
@@ -4969,16 +4957,16 @@
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>PMP1270485</t>
+          <t>PMP1270486</t>
         </is>
       </c>
       <c r="E225" s="6" t="n">
-        <v>24112073</v>
+        <v>1848014</v>
       </c>
       <c r="F225" s="10" t="inlineStr"/>
       <c r="G225" s="10" t="inlineStr"/>
       <c r="H225" s="6" t="n">
-        <v>24112073</v>
+        <v>1848014</v>
       </c>
       <c r="I225" s="11" t="inlineStr"/>
     </row>
@@ -4990,16 +4978,16 @@
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>PMP1270486</t>
+          <t>PMP1270487</t>
         </is>
       </c>
       <c r="E226" s="6" t="n">
-        <v>1848014</v>
+        <v>6441615</v>
       </c>
       <c r="F226" s="10" t="inlineStr"/>
       <c r="G226" s="10" t="inlineStr"/>
       <c r="H226" s="6" t="n">
-        <v>1848014</v>
+        <v>6441615</v>
       </c>
       <c r="I226" s="11" t="inlineStr"/>
     </row>
@@ -5011,16 +4999,16 @@
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>PMP1270487</t>
+          <t>PMP1270488</t>
         </is>
       </c>
       <c r="E227" s="6" t="n">
-        <v>6441615</v>
+        <v>41274053</v>
       </c>
       <c r="F227" s="10" t="inlineStr"/>
       <c r="G227" s="10" t="inlineStr"/>
       <c r="H227" s="6" t="n">
-        <v>6441615</v>
+        <v>41274053</v>
       </c>
       <c r="I227" s="11" t="inlineStr"/>
     </row>
@@ -5032,16 +5020,16 @@
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>PMP1270488</t>
+          <t>PMP1270544</t>
         </is>
       </c>
       <c r="E228" s="6" t="n">
-        <v>41274053</v>
+        <v>54038897</v>
       </c>
       <c r="F228" s="10" t="inlineStr"/>
       <c r="G228" s="10" t="inlineStr"/>
       <c r="H228" s="6" t="n">
-        <v>41274053</v>
+        <v>54038897</v>
       </c>
       <c r="I228" s="11" t="inlineStr"/>
     </row>
@@ -5053,16 +5041,16 @@
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>PMP1270544</t>
+          <t>PMP1270545</t>
         </is>
       </c>
       <c r="E229" s="6" t="n">
-        <v>54038897</v>
+        <v>5513672</v>
       </c>
       <c r="F229" s="10" t="inlineStr"/>
       <c r="G229" s="10" t="inlineStr"/>
       <c r="H229" s="6" t="n">
-        <v>54038897</v>
+        <v>5513672</v>
       </c>
       <c r="I229" s="11" t="inlineStr"/>
     </row>
@@ -5074,16 +5062,16 @@
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>PMP1270545</t>
+          <t>PMP1270546</t>
         </is>
       </c>
       <c r="E230" s="6" t="n">
-        <v>5513672</v>
+        <v>1478411</v>
       </c>
       <c r="F230" s="10" t="inlineStr"/>
       <c r="G230" s="10" t="inlineStr"/>
       <c r="H230" s="6" t="n">
-        <v>5513672</v>
+        <v>1478411</v>
       </c>
       <c r="I230" s="11" t="inlineStr"/>
     </row>
@@ -5095,16 +5083,16 @@
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>PMP1270546</t>
+          <t>PMP1270547</t>
         </is>
       </c>
       <c r="E231" s="6" t="n">
-        <v>1478411</v>
+        <v>36069932</v>
       </c>
       <c r="F231" s="10" t="inlineStr"/>
       <c r="G231" s="10" t="inlineStr"/>
       <c r="H231" s="6" t="n">
-        <v>1478411</v>
+        <v>36069932</v>
       </c>
       <c r="I231" s="11" t="inlineStr"/>
     </row>
@@ -5116,16 +5104,16 @@
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>PMP1270547</t>
+          <t>PMP1270548</t>
         </is>
       </c>
       <c r="E232" s="6" t="n">
-        <v>36069932</v>
+        <v>21135960</v>
       </c>
       <c r="F232" s="10" t="inlineStr"/>
       <c r="G232" s="10" t="inlineStr"/>
       <c r="H232" s="6" t="n">
-        <v>36069932</v>
+        <v>21135960</v>
       </c>
       <c r="I232" s="11" t="inlineStr"/>
     </row>
@@ -5137,16 +5125,16 @@
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>PMP1270548</t>
+          <t>PMP1270549</t>
         </is>
       </c>
       <c r="E233" s="6" t="n">
-        <v>21135960</v>
+        <v>64202726</v>
       </c>
       <c r="F233" s="10" t="inlineStr"/>
       <c r="G233" s="10" t="inlineStr"/>
       <c r="H233" s="6" t="n">
-        <v>21135960</v>
+        <v>64202726</v>
       </c>
       <c r="I233" s="11" t="inlineStr"/>
     </row>
@@ -5158,16 +5146,16 @@
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>PMP1270549</t>
+          <t>PMP1270550</t>
         </is>
       </c>
       <c r="E234" s="6" t="n">
-        <v>64202726</v>
+        <v>3834662</v>
       </c>
       <c r="F234" s="10" t="inlineStr"/>
       <c r="G234" s="10" t="inlineStr"/>
       <c r="H234" s="6" t="n">
-        <v>64202726</v>
+        <v>3834662</v>
       </c>
       <c r="I234" s="11" t="inlineStr"/>
     </row>
@@ -5179,16 +5167,16 @@
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>PMP1270550</t>
+          <t>PMP1270551</t>
         </is>
       </c>
       <c r="E235" s="6" t="n">
-        <v>3834662</v>
+        <v>3930349</v>
       </c>
       <c r="F235" s="10" t="inlineStr"/>
       <c r="G235" s="10" t="inlineStr"/>
       <c r="H235" s="6" t="n">
-        <v>3834662</v>
+        <v>3930349</v>
       </c>
       <c r="I235" s="11" t="inlineStr"/>
     </row>
@@ -5200,16 +5188,16 @@
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>PMP1270551</t>
+          <t>PMP1270552</t>
         </is>
       </c>
       <c r="E236" s="6" t="n">
-        <v>3930349</v>
+        <v>111850295</v>
       </c>
       <c r="F236" s="10" t="inlineStr"/>
       <c r="G236" s="10" t="inlineStr"/>
       <c r="H236" s="6" t="n">
-        <v>3930349</v>
+        <v>111850295</v>
       </c>
       <c r="I236" s="11" t="inlineStr"/>
     </row>
@@ -5221,16 +5209,16 @@
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>PMP1270552</t>
+          <t>PMP1270696</t>
         </is>
       </c>
       <c r="E237" s="6" t="n">
-        <v>111850295</v>
+        <v>35335923</v>
       </c>
       <c r="F237" s="10" t="inlineStr"/>
       <c r="G237" s="10" t="inlineStr"/>
       <c r="H237" s="6" t="n">
-        <v>111850295</v>
+        <v>35335923</v>
       </c>
       <c r="I237" s="11" t="inlineStr"/>
     </row>
@@ -5242,16 +5230,16 @@
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>PMP1270696</t>
+          <t>PMP1270697</t>
         </is>
       </c>
       <c r="E238" s="6" t="n">
-        <v>35335923</v>
+        <v>5053475</v>
       </c>
       <c r="F238" s="10" t="inlineStr"/>
       <c r="G238" s="10" t="inlineStr"/>
       <c r="H238" s="6" t="n">
-        <v>35335923</v>
+        <v>5053475</v>
       </c>
       <c r="I238" s="11" t="inlineStr"/>
     </row>
@@ -5263,16 +5251,16 @@
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>PMP1270697</t>
+          <t>PMP1270698</t>
         </is>
       </c>
       <c r="E239" s="6" t="n">
-        <v>5053475</v>
+        <v>5457341</v>
       </c>
       <c r="F239" s="10" t="inlineStr"/>
       <c r="G239" s="10" t="inlineStr"/>
       <c r="H239" s="6" t="n">
-        <v>5053475</v>
+        <v>5457341</v>
       </c>
       <c r="I239" s="11" t="inlineStr"/>
     </row>
@@ -5284,16 +5272,16 @@
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>PMP1270698</t>
+          <t>PMP1270699</t>
         </is>
       </c>
       <c r="E240" s="6" t="n">
-        <v>5457341</v>
+        <v>284892693</v>
       </c>
       <c r="F240" s="10" t="inlineStr"/>
       <c r="G240" s="10" t="inlineStr"/>
       <c r="H240" s="6" t="n">
-        <v>5457341</v>
+        <v>284892693</v>
       </c>
       <c r="I240" s="11" t="inlineStr"/>
     </row>
@@ -5305,16 +5293,16 @@
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>PMP1270699</t>
+          <t>PMP1270700</t>
         </is>
       </c>
       <c r="E241" s="6" t="n">
-        <v>284892693</v>
+        <v>9344757</v>
       </c>
       <c r="F241" s="10" t="inlineStr"/>
       <c r="G241" s="10" t="inlineStr"/>
       <c r="H241" s="6" t="n">
-        <v>284892693</v>
+        <v>9344757</v>
       </c>
       <c r="I241" s="11" t="inlineStr"/>
     </row>
@@ -5326,16 +5314,16 @@
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>PMP1270700</t>
+          <t>PMP1271252</t>
         </is>
       </c>
       <c r="E242" s="6" t="n">
-        <v>9344757</v>
+        <v>122788016</v>
       </c>
       <c r="F242" s="10" t="inlineStr"/>
       <c r="G242" s="10" t="inlineStr"/>
       <c r="H242" s="6" t="n">
-        <v>9344757</v>
+        <v>122788016</v>
       </c>
       <c r="I242" s="11" t="inlineStr"/>
     </row>
@@ -5347,16 +5335,16 @@
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>PMP1271252</t>
+          <t>PMP1271253</t>
         </is>
       </c>
       <c r="E243" s="6" t="n">
-        <v>122788016</v>
+        <v>161789861</v>
       </c>
       <c r="F243" s="10" t="inlineStr"/>
       <c r="G243" s="10" t="inlineStr"/>
       <c r="H243" s="6" t="n">
-        <v>122788016</v>
+        <v>161789861</v>
       </c>
       <c r="I243" s="11" t="inlineStr"/>
     </row>
@@ -5368,16 +5356,16 @@
       </c>
       <c r="D244" s="10" t="inlineStr">
         <is>
-          <t>PMP1271253</t>
+          <t>PMP1271709</t>
         </is>
       </c>
       <c r="E244" s="6" t="n">
-        <v>161789861</v>
+        <v>85550123</v>
       </c>
       <c r="F244" s="10" t="inlineStr"/>
       <c r="G244" s="10" t="inlineStr"/>
       <c r="H244" s="6" t="n">
-        <v>161789861</v>
+        <v>85550123</v>
       </c>
       <c r="I244" s="11" t="inlineStr"/>
     </row>
@@ -5389,16 +5377,16 @@
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>PMP1271709</t>
+          <t>PMP1271710</t>
         </is>
       </c>
       <c r="E245" s="6" t="n">
-        <v>85550123</v>
+        <v>52128430</v>
       </c>
       <c r="F245" s="10" t="inlineStr"/>
       <c r="G245" s="10" t="inlineStr"/>
       <c r="H245" s="6" t="n">
-        <v>85550123</v>
+        <v>52128430</v>
       </c>
       <c r="I245" s="11" t="inlineStr"/>
     </row>
@@ -5410,16 +5398,16 @@
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>PMP1271710</t>
+          <t>PMP1271711</t>
         </is>
       </c>
       <c r="E246" s="6" t="n">
-        <v>52128430</v>
+        <v>15456830</v>
       </c>
       <c r="F246" s="10" t="inlineStr"/>
       <c r="G246" s="10" t="inlineStr"/>
       <c r="H246" s="6" t="n">
-        <v>52128430</v>
+        <v>15456830</v>
       </c>
       <c r="I246" s="11" t="inlineStr"/>
     </row>
@@ -5431,16 +5419,16 @@
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>PMP1271711</t>
+          <t>PMP1271712</t>
         </is>
       </c>
       <c r="E247" s="6" t="n">
-        <v>15456830</v>
+        <v>75193282</v>
       </c>
       <c r="F247" s="10" t="inlineStr"/>
       <c r="G247" s="10" t="inlineStr"/>
       <c r="H247" s="6" t="n">
-        <v>15456830</v>
+        <v>75193282</v>
       </c>
       <c r="I247" s="11" t="inlineStr"/>
     </row>
@@ -5452,39 +5440,51 @@
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>PMP1271712</t>
+          <t>PMP1271713</t>
         </is>
       </c>
       <c r="E248" s="6" t="n">
-        <v>75193282</v>
+        <v>184801</v>
       </c>
       <c r="F248" s="10" t="inlineStr"/>
       <c r="G248" s="10" t="inlineStr"/>
       <c r="H248" s="6" t="n">
-        <v>75193282</v>
+        <v>184801</v>
       </c>
       <c r="I248" s="11" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="C249" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>PMP1271713</t>
+          <t>PMP1266600</t>
         </is>
       </c>
       <c r="E249" s="6" t="n">
-        <v>184801</v>
-      </c>
-      <c r="F249" s="10" t="inlineStr"/>
-      <c r="G249" s="10" t="inlineStr"/>
+        <v>-558395</v>
+      </c>
+      <c r="F249" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G249" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
       <c r="H249" s="6" t="n">
-        <v>184801</v>
-      </c>
-      <c r="I249" s="11" t="inlineStr"/>
+        <v>-558395</v>
+      </c>
+      <c r="I249" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1266600</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="C250" s="10" t="inlineStr">
@@ -5494,28 +5494,28 @@
       </c>
       <c r="D250" s="10" t="inlineStr">
         <is>
-          <t>Costo de Transferen</t>
+          <t>PMP1266608</t>
         </is>
       </c>
       <c r="E250" s="6" t="n">
-        <v>-3000</v>
+        <v>-255997</v>
       </c>
       <c r="F250" s="10" t="inlineStr">
         <is>
-          <t>Costo de Transferen</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G250" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H250" s="6" t="n">
-        <v>-3000</v>
+        <v>-255997</v>
       </c>
       <c r="I250" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Rechazo PMP1266608</t>
         </is>
       </c>
     </row>
@@ -5527,28 +5527,28 @@
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1266649</t>
         </is>
       </c>
       <c r="E251" s="6" t="n">
-        <v>-161133</v>
+        <v>-585560</v>
       </c>
       <c r="F251" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G251" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H251" s="6" t="n">
-        <v>-161133</v>
+        <v>-585560</v>
       </c>
       <c r="I251" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.196.186 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1266649</t>
         </is>
       </c>
     </row>
@@ -5560,28 +5560,28 @@
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO COMPRAS</t>
+          <t>PMP1266658</t>
         </is>
       </c>
       <c r="E252" s="6" t="n">
-        <v>-582054</v>
+        <v>-156659</v>
       </c>
       <c r="F252" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G252" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H252" s="6" t="n">
-        <v>-582054</v>
+        <v>-156659</v>
       </c>
       <c r="I252" s="11" t="inlineStr">
         <is>
-          <t>DCC DSCTO 20.222.600.126.372 DESCUENTO COMPRAS PLATOS</t>
+          <t>Rechazo PMP1266658</t>
         </is>
       </c>
     </row>
@@ -5593,28 +5593,28 @@
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>PMP1266661</t>
         </is>
       </c>
       <c r="E253" s="6" t="n">
-        <v>-6240707</v>
+        <v>-1151504</v>
       </c>
       <c r="F253" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G253" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H253" s="6" t="n">
-        <v>-6240707</v>
+        <v>-1151504</v>
       </c>
       <c r="I253" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO 20.171.100.014.225 DEVOLUCIONES DROGUE</t>
+          <t>Rechazo PMP1266661</t>
         </is>
       </c>
     </row>
@@ -5626,28 +5626,28 @@
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>PMP1266688</t>
         </is>
       </c>
       <c r="E254" s="6" t="n">
-        <v>-479755</v>
+        <v>-183068</v>
       </c>
       <c r="F254" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G254" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H254" s="6" t="n">
-        <v>-479755</v>
+        <v>-183068</v>
       </c>
       <c r="I254" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO 20.181.100.045.651 DEVOLUCIONES DROGUE</t>
+          <t>Rechazo PMP1266688</t>
         </is>
       </c>
     </row>
@@ -5659,28 +5659,28 @@
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>PMP1266825</t>
         </is>
       </c>
       <c r="E255" s="6" t="n">
-        <v>-4357583</v>
+        <v>-1082492</v>
       </c>
       <c r="F255" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G255" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H255" s="6" t="n">
-        <v>-4357583</v>
+        <v>-1082492</v>
       </c>
       <c r="I255" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO 20.171.200.014.220 DEVOLUCIONES PERFUME</t>
+          <t>Rechazo PMP1266825</t>
         </is>
       </c>
     </row>
@@ -5692,28 +5692,28 @@
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1266827</t>
         </is>
       </c>
       <c r="E256" s="6" t="n">
-        <v>-72808231</v>
+        <v>-690674</v>
       </c>
       <c r="F256" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G256" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H256" s="6" t="n">
-        <v>-72808231</v>
+        <v>-690674</v>
       </c>
       <c r="I256" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.171.100.014.225 DSTO COMERCIAL FIJO DROGUE</t>
+          <t>Rechazo PMP1266827</t>
         </is>
       </c>
     </row>
@@ -5725,28 +5725,28 @@
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1266968</t>
         </is>
       </c>
       <c r="E257" s="6" t="n">
-        <v>-7813296</v>
+        <v>-354801</v>
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G257" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H257" s="6" t="n">
-        <v>-7813296</v>
+        <v>-354801</v>
       </c>
       <c r="I257" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.181.100.032.054 DSTO COMERCIAL FIJO DROGUE</t>
+          <t>Rechazo PMP1266968</t>
         </is>
       </c>
     </row>
@@ -5758,28 +5758,28 @@
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1266972</t>
         </is>
       </c>
       <c r="E258" s="6" t="n">
-        <v>-8795517</v>
+        <v>-644654</v>
       </c>
       <c r="F258" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G258" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H258" s="6" t="n">
-        <v>-8795517</v>
+        <v>-644654</v>
       </c>
       <c r="I258" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.181.100.045.651 DSTO COMERCIAL FIJO DROGUE</t>
+          <t>Rechazo PMP1266972</t>
         </is>
       </c>
     </row>
@@ -5791,28 +5791,28 @@
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1266975</t>
         </is>
       </c>
       <c r="E259" s="6" t="n">
-        <v>-101676935</v>
+        <v>-91512</v>
       </c>
       <c r="F259" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G259" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H259" s="6" t="n">
-        <v>-101676935</v>
+        <v>-91512</v>
       </c>
       <c r="I259" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.171.200.014.220 DSTO COMERCIAL FIJO PERFUME</t>
+          <t>Rechazo PMP1266975</t>
         </is>
       </c>
     </row>
@@ -5824,28 +5824,28 @@
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1266976</t>
         </is>
       </c>
       <c r="E260" s="6" t="n">
-        <v>-92620002</v>
+        <v>-2127332</v>
       </c>
       <c r="F260" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G260" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H260" s="6" t="n">
-        <v>-92620002</v>
+        <v>-2127332</v>
       </c>
       <c r="I260" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.181.200.033.536 DSTO COMERCIAL FIJO PERFUME</t>
+          <t>Rechazo PMP1266976</t>
         </is>
       </c>
     </row>
@@ -5857,28 +5857,28 @@
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1266978</t>
         </is>
       </c>
       <c r="E261" s="6" t="n">
-        <v>-8730793</v>
+        <v>-392009</v>
       </c>
       <c r="F261" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G261" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H261" s="6" t="n">
-        <v>-8730793</v>
+        <v>-392009</v>
       </c>
       <c r="I261" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.222.600.126.372 DSTO COMERCIAL FIJO PLATOS</t>
+          <t>Rechazo PMP1266978</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>PMP1266600</t>
+          <t>PMP1267041</t>
         </is>
       </c>
       <c r="E262" s="6" t="n">
-        <v>-558395</v>
+        <v>-1700629</v>
       </c>
       <c r="F262" s="10" t="inlineStr">
         <is>
@@ -5907,11 +5907,11 @@
         </is>
       </c>
       <c r="H262" s="6" t="n">
-        <v>-558395</v>
+        <v>-1700629</v>
       </c>
       <c r="I262" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266600</t>
+          <t>Rechazo PMP1267041</t>
         </is>
       </c>
     </row>
@@ -5923,11 +5923,11 @@
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>PMP1266608</t>
+          <t>PMP1267042</t>
         </is>
       </c>
       <c r="E263" s="6" t="n">
-        <v>-255997</v>
+        <v>-13923399</v>
       </c>
       <c r="F263" s="10" t="inlineStr">
         <is>
@@ -5940,11 +5940,11 @@
         </is>
       </c>
       <c r="H263" s="6" t="n">
-        <v>-255997</v>
+        <v>-13923399</v>
       </c>
       <c r="I263" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266608</t>
+          <t>Rechazo PMP1267042</t>
         </is>
       </c>
     </row>
@@ -5956,11 +5956,11 @@
       </c>
       <c r="D264" s="10" t="inlineStr">
         <is>
-          <t>PMP1266649</t>
+          <t>PMP1267186</t>
         </is>
       </c>
       <c r="E264" s="6" t="n">
-        <v>-585560</v>
+        <v>-1247498</v>
       </c>
       <c r="F264" s="10" t="inlineStr">
         <is>
@@ -5973,11 +5973,11 @@
         </is>
       </c>
       <c r="H264" s="6" t="n">
-        <v>-585560</v>
+        <v>-1247498</v>
       </c>
       <c r="I264" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266649</t>
+          <t>Rechazo PMP1267186</t>
         </is>
       </c>
     </row>
@@ -5989,11 +5989,11 @@
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>PMP1266658</t>
+          <t>PMP1267318</t>
         </is>
       </c>
       <c r="E265" s="6" t="n">
-        <v>-156659</v>
+        <v>-279548</v>
       </c>
       <c r="F265" s="10" t="inlineStr">
         <is>
@@ -6006,11 +6006,11 @@
         </is>
       </c>
       <c r="H265" s="6" t="n">
-        <v>-156659</v>
+        <v>-279548</v>
       </c>
       <c r="I265" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266658</t>
+          <t>Rechazo PMP1267318</t>
         </is>
       </c>
     </row>
@@ -6022,11 +6022,11 @@
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>PMP1266661</t>
+          <t>PMP1267320</t>
         </is>
       </c>
       <c r="E266" s="6" t="n">
-        <v>-1151504</v>
+        <v>-266591</v>
       </c>
       <c r="F266" s="10" t="inlineStr">
         <is>
@@ -6039,11 +6039,11 @@
         </is>
       </c>
       <c r="H266" s="6" t="n">
-        <v>-1151504</v>
+        <v>-266591</v>
       </c>
       <c r="I266" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266661</t>
+          <t>Rechazo PMP1267320</t>
         </is>
       </c>
     </row>
@@ -6055,11 +6055,11 @@
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>PMP1266688</t>
+          <t>PMP1267438</t>
         </is>
       </c>
       <c r="E267" s="6" t="n">
-        <v>-183068</v>
+        <v>-335886</v>
       </c>
       <c r="F267" s="10" t="inlineStr">
         <is>
@@ -6072,11 +6072,11 @@
         </is>
       </c>
       <c r="H267" s="6" t="n">
-        <v>-183068</v>
+        <v>-335886</v>
       </c>
       <c r="I267" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266688</t>
+          <t>Rechazo PMP1267438</t>
         </is>
       </c>
     </row>
@@ -6088,11 +6088,11 @@
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>PMP1266825</t>
+          <t>PMP1267583</t>
         </is>
       </c>
       <c r="E268" s="6" t="n">
-        <v>-1082492</v>
+        <v>-202495</v>
       </c>
       <c r="F268" s="10" t="inlineStr">
         <is>
@@ -6105,11 +6105,11 @@
         </is>
       </c>
       <c r="H268" s="6" t="n">
-        <v>-1082492</v>
+        <v>-202495</v>
       </c>
       <c r="I268" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266825</t>
+          <t>Rechazo PMP1267583</t>
         </is>
       </c>
     </row>
@@ -6121,11 +6121,11 @@
       </c>
       <c r="D269" s="10" t="inlineStr">
         <is>
-          <t>PMP1266827</t>
+          <t>PMP1268024</t>
         </is>
       </c>
       <c r="E269" s="6" t="n">
-        <v>-690674</v>
+        <v>-94999</v>
       </c>
       <c r="F269" s="10" t="inlineStr">
         <is>
@@ -6138,11 +6138,11 @@
         </is>
       </c>
       <c r="H269" s="6" t="n">
-        <v>-690674</v>
+        <v>-94999</v>
       </c>
       <c r="I269" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266827</t>
+          <t>Rechazo PMP1268024</t>
         </is>
       </c>
     </row>
@@ -6154,11 +6154,11 @@
       </c>
       <c r="D270" s="10" t="inlineStr">
         <is>
-          <t>PMP1266968</t>
+          <t>PMP1268027</t>
         </is>
       </c>
       <c r="E270" s="6" t="n">
-        <v>-354801</v>
+        <v>-254399</v>
       </c>
       <c r="F270" s="10" t="inlineStr">
         <is>
@@ -6171,11 +6171,11 @@
         </is>
       </c>
       <c r="H270" s="6" t="n">
-        <v>-354801</v>
+        <v>-254399</v>
       </c>
       <c r="I270" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266968</t>
+          <t>Rechazo PMP1268027</t>
         </is>
       </c>
     </row>
@@ -6187,11 +6187,11 @@
       </c>
       <c r="D271" s="10" t="inlineStr">
         <is>
-          <t>PMP1266972</t>
+          <t>PMP1268608</t>
         </is>
       </c>
       <c r="E271" s="6" t="n">
-        <v>-644654</v>
+        <v>-295395</v>
       </c>
       <c r="F271" s="10" t="inlineStr">
         <is>
@@ -6204,11 +6204,11 @@
         </is>
       </c>
       <c r="H271" s="6" t="n">
-        <v>-644654</v>
+        <v>-295395</v>
       </c>
       <c r="I271" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266972</t>
+          <t>Rechazo PMP1268608</t>
         </is>
       </c>
     </row>
@@ -6220,11 +6220,11 @@
       </c>
       <c r="D272" s="10" t="inlineStr">
         <is>
-          <t>PMP1266975</t>
+          <t>PMP1268642</t>
         </is>
       </c>
       <c r="E272" s="6" t="n">
-        <v>-91512</v>
+        <v>-27504570</v>
       </c>
       <c r="F272" s="10" t="inlineStr">
         <is>
@@ -6237,11 +6237,11 @@
         </is>
       </c>
       <c r="H272" s="6" t="n">
-        <v>-91512</v>
+        <v>-27504570</v>
       </c>
       <c r="I272" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266975</t>
+          <t>Rechazo PMP1268642</t>
         </is>
       </c>
     </row>
@@ -6253,11 +6253,11 @@
       </c>
       <c r="D273" s="10" t="inlineStr">
         <is>
-          <t>PMP1266976</t>
+          <t>PMP1268643</t>
         </is>
       </c>
       <c r="E273" s="6" t="n">
-        <v>-2127332</v>
+        <v>-121691</v>
       </c>
       <c r="F273" s="10" t="inlineStr">
         <is>
@@ -6270,11 +6270,11 @@
         </is>
       </c>
       <c r="H273" s="6" t="n">
-        <v>-2127332</v>
+        <v>-121691</v>
       </c>
       <c r="I273" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266976</t>
+          <t>Rechazo PMP1268643</t>
         </is>
       </c>
     </row>
@@ -6286,11 +6286,11 @@
       </c>
       <c r="D274" s="10" t="inlineStr">
         <is>
-          <t>PMP1266978</t>
+          <t>PMP1268714</t>
         </is>
       </c>
       <c r="E274" s="6" t="n">
-        <v>-392009</v>
+        <v>-3903909</v>
       </c>
       <c r="F274" s="10" t="inlineStr">
         <is>
@@ -6303,11 +6303,11 @@
         </is>
       </c>
       <c r="H274" s="6" t="n">
-        <v>-392009</v>
+        <v>-3903909</v>
       </c>
       <c r="I274" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1266978</t>
+          <t>Rechazo PMP1268714</t>
         </is>
       </c>
     </row>
@@ -6319,11 +6319,11 @@
       </c>
       <c r="D275" s="10" t="inlineStr">
         <is>
-          <t>PMP1267041</t>
+          <t>PMP1268746</t>
         </is>
       </c>
       <c r="E275" s="6" t="n">
-        <v>-1700629</v>
+        <v>-1450365</v>
       </c>
       <c r="F275" s="10" t="inlineStr">
         <is>
@@ -6336,11 +6336,11 @@
         </is>
       </c>
       <c r="H275" s="6" t="n">
-        <v>-1700629</v>
+        <v>-1450365</v>
       </c>
       <c r="I275" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267041</t>
+          <t>Rechazo PMP1268746</t>
         </is>
       </c>
     </row>
@@ -6352,11 +6352,11 @@
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>PMP1267042</t>
+          <t>PMP1268759</t>
         </is>
       </c>
       <c r="E276" s="6" t="n">
-        <v>-13923399</v>
+        <v>-344952</v>
       </c>
       <c r="F276" s="10" t="inlineStr">
         <is>
@@ -6369,11 +6369,11 @@
         </is>
       </c>
       <c r="H276" s="6" t="n">
-        <v>-13923399</v>
+        <v>-344952</v>
       </c>
       <c r="I276" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267042</t>
+          <t>Rechazo PMP1268759</t>
         </is>
       </c>
     </row>
@@ -6385,11 +6385,11 @@
       </c>
       <c r="D277" s="10" t="inlineStr">
         <is>
-          <t>PMP1267186</t>
+          <t>PMP1269679</t>
         </is>
       </c>
       <c r="E277" s="6" t="n">
-        <v>-1247498</v>
+        <v>-1172865</v>
       </c>
       <c r="F277" s="10" t="inlineStr">
         <is>
@@ -6402,11 +6402,11 @@
         </is>
       </c>
       <c r="H277" s="6" t="n">
-        <v>-1247498</v>
+        <v>-1172865</v>
       </c>
       <c r="I277" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267186</t>
+          <t>Rechazo PMP1269679</t>
         </is>
       </c>
     </row>
@@ -6418,11 +6418,11 @@
       </c>
       <c r="D278" s="10" t="inlineStr">
         <is>
-          <t>PMP1267318</t>
+          <t>PMP1269681</t>
         </is>
       </c>
       <c r="E278" s="6" t="n">
-        <v>-279548</v>
+        <v>-6085186</v>
       </c>
       <c r="F278" s="10" t="inlineStr">
         <is>
@@ -6435,11 +6435,11 @@
         </is>
       </c>
       <c r="H278" s="6" t="n">
-        <v>-279548</v>
+        <v>-6085186</v>
       </c>
       <c r="I278" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267318</t>
+          <t>Rechazo PMP1269681</t>
         </is>
       </c>
     </row>
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D279" s="10" t="inlineStr">
         <is>
-          <t>PMP1267320</t>
+          <t>PMP1269709</t>
         </is>
       </c>
       <c r="E279" s="6" t="n">
-        <v>-266591</v>
+        <v>-846601</v>
       </c>
       <c r="F279" s="10" t="inlineStr">
         <is>
@@ -6468,11 +6468,11 @@
         </is>
       </c>
       <c r="H279" s="6" t="n">
-        <v>-266591</v>
+        <v>-846601</v>
       </c>
       <c r="I279" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267320</t>
+          <t>Rechazo PMP1269709</t>
         </is>
       </c>
     </row>
@@ -6484,11 +6484,11 @@
       </c>
       <c r="D280" s="10" t="inlineStr">
         <is>
-          <t>PMP1267438</t>
+          <t>PMP1269710</t>
         </is>
       </c>
       <c r="E280" s="6" t="n">
-        <v>-335886</v>
+        <v>-82421</v>
       </c>
       <c r="F280" s="10" t="inlineStr">
         <is>
@@ -6501,11 +6501,11 @@
         </is>
       </c>
       <c r="H280" s="6" t="n">
-        <v>-335886</v>
+        <v>-82421</v>
       </c>
       <c r="I280" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267438</t>
+          <t>Rechazo PMP1269710</t>
         </is>
       </c>
     </row>
@@ -6517,11 +6517,11 @@
       </c>
       <c r="D281" s="10" t="inlineStr">
         <is>
-          <t>PMP1267583</t>
+          <t>PMP1269725</t>
         </is>
       </c>
       <c r="E281" s="6" t="n">
-        <v>-202495</v>
+        <v>-19608</v>
       </c>
       <c r="F281" s="10" t="inlineStr">
         <is>
@@ -6534,11 +6534,11 @@
         </is>
       </c>
       <c r="H281" s="6" t="n">
-        <v>-202495</v>
+        <v>-19608</v>
       </c>
       <c r="I281" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1267583</t>
+          <t>Rechazo PMP1269725</t>
         </is>
       </c>
     </row>
@@ -6550,11 +6550,11 @@
       </c>
       <c r="D282" s="10" t="inlineStr">
         <is>
-          <t>PMP1268024</t>
+          <t>PMP1269740</t>
         </is>
       </c>
       <c r="E282" s="6" t="n">
-        <v>-94999</v>
+        <v>-887036</v>
       </c>
       <c r="F282" s="10" t="inlineStr">
         <is>
@@ -6567,11 +6567,11 @@
         </is>
       </c>
       <c r="H282" s="6" t="n">
-        <v>-94999</v>
+        <v>-887036</v>
       </c>
       <c r="I282" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268024</t>
+          <t>Rechazo PMP1269740</t>
         </is>
       </c>
     </row>
@@ -6583,11 +6583,11 @@
       </c>
       <c r="D283" s="10" t="inlineStr">
         <is>
-          <t>PMP1268027</t>
+          <t>PMP1269787</t>
         </is>
       </c>
       <c r="E283" s="6" t="n">
-        <v>-254399</v>
+        <v>-279182</v>
       </c>
       <c r="F283" s="10" t="inlineStr">
         <is>
@@ -6600,11 +6600,11 @@
         </is>
       </c>
       <c r="H283" s="6" t="n">
-        <v>-254399</v>
+        <v>-279182</v>
       </c>
       <c r="I283" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268027</t>
+          <t>Rechazo PMP1269787</t>
         </is>
       </c>
     </row>
@@ -6616,11 +6616,11 @@
       </c>
       <c r="D284" s="10" t="inlineStr">
         <is>
-          <t>PMP1268608</t>
+          <t>PMP1269999</t>
         </is>
       </c>
       <c r="E284" s="6" t="n">
-        <v>-295395</v>
+        <v>-87001</v>
       </c>
       <c r="F284" s="10" t="inlineStr">
         <is>
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="H284" s="6" t="n">
-        <v>-295395</v>
+        <v>-87001</v>
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268608</t>
+          <t>Rechazo PMP1269999</t>
         </is>
       </c>
     </row>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="D285" s="10" t="inlineStr">
         <is>
-          <t>PMP1268642</t>
+          <t>PMP1270057</t>
         </is>
       </c>
       <c r="E285" s="6" t="n">
-        <v>-27504570</v>
+        <v>-1980306</v>
       </c>
       <c r="F285" s="10" t="inlineStr">
         <is>
@@ -6666,11 +6666,11 @@
         </is>
       </c>
       <c r="H285" s="6" t="n">
-        <v>-27504570</v>
+        <v>-1980306</v>
       </c>
       <c r="I285" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268642</t>
+          <t>Rechazo PMP1270057</t>
         </is>
       </c>
     </row>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="D286" s="10" t="inlineStr">
         <is>
-          <t>PMP1268643</t>
+          <t>PMP1270059</t>
         </is>
       </c>
       <c r="E286" s="6" t="n">
-        <v>-121691</v>
+        <v>-1091682</v>
       </c>
       <c r="F286" s="10" t="inlineStr">
         <is>
@@ -6699,11 +6699,11 @@
         </is>
       </c>
       <c r="H286" s="6" t="n">
-        <v>-121691</v>
+        <v>-1091682</v>
       </c>
       <c r="I286" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268643</t>
+          <t>Rechazo PMP1270059</t>
         </is>
       </c>
     </row>
@@ -6715,11 +6715,11 @@
       </c>
       <c r="D287" s="10" t="inlineStr">
         <is>
-          <t>PMP1268714</t>
+          <t>PMP1270062</t>
         </is>
       </c>
       <c r="E287" s="6" t="n">
-        <v>-3903909</v>
+        <v>-107500</v>
       </c>
       <c r="F287" s="10" t="inlineStr">
         <is>
@@ -6732,11 +6732,11 @@
         </is>
       </c>
       <c r="H287" s="6" t="n">
-        <v>-3903909</v>
+        <v>-107500</v>
       </c>
       <c r="I287" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268714</t>
+          <t>Rechazo PMP1270062</t>
         </is>
       </c>
     </row>
@@ -6748,11 +6748,11 @@
       </c>
       <c r="D288" s="10" t="inlineStr">
         <is>
-          <t>PMP1268746</t>
+          <t>PMP1270069</t>
         </is>
       </c>
       <c r="E288" s="6" t="n">
-        <v>-1450365</v>
+        <v>-1769895</v>
       </c>
       <c r="F288" s="10" t="inlineStr">
         <is>
@@ -6765,11 +6765,11 @@
         </is>
       </c>
       <c r="H288" s="6" t="n">
-        <v>-1450365</v>
+        <v>-1769895</v>
       </c>
       <c r="I288" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268746</t>
+          <t>Rechazo PMP1270069</t>
         </is>
       </c>
     </row>
@@ -6781,11 +6781,11 @@
       </c>
       <c r="D289" s="10" t="inlineStr">
         <is>
-          <t>PMP1268759</t>
+          <t>PMP1270070</t>
         </is>
       </c>
       <c r="E289" s="6" t="n">
-        <v>-344952</v>
+        <v>-35598445</v>
       </c>
       <c r="F289" s="10" t="inlineStr">
         <is>
@@ -6798,11 +6798,11 @@
         </is>
       </c>
       <c r="H289" s="6" t="n">
-        <v>-344952</v>
+        <v>-35598445</v>
       </c>
       <c r="I289" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1268759</t>
+          <t>Rechazo PMP1270070</t>
         </is>
       </c>
     </row>
@@ -6814,11 +6814,11 @@
       </c>
       <c r="D290" s="10" t="inlineStr">
         <is>
-          <t>PMP1269679</t>
+          <t>PMP1270075</t>
         </is>
       </c>
       <c r="E290" s="6" t="n">
-        <v>-1172865</v>
+        <v>-1063192</v>
       </c>
       <c r="F290" s="10" t="inlineStr">
         <is>
@@ -6831,11 +6831,11 @@
         </is>
       </c>
       <c r="H290" s="6" t="n">
-        <v>-1172865</v>
+        <v>-1063192</v>
       </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269679</t>
+          <t>Rechazo PMP1270075</t>
         </is>
       </c>
     </row>
@@ -6847,11 +6847,11 @@
       </c>
       <c r="D291" s="10" t="inlineStr">
         <is>
-          <t>PMP1269681</t>
+          <t>PMP1270081</t>
         </is>
       </c>
       <c r="E291" s="6" t="n">
-        <v>-6085186</v>
+        <v>-287167</v>
       </c>
       <c r="F291" s="10" t="inlineStr">
         <is>
@@ -6864,11 +6864,11 @@
         </is>
       </c>
       <c r="H291" s="6" t="n">
-        <v>-6085186</v>
+        <v>-287167</v>
       </c>
       <c r="I291" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269681</t>
+          <t>Rechazo PMP1270081</t>
         </is>
       </c>
     </row>
@@ -6880,11 +6880,11 @@
       </c>
       <c r="D292" s="10" t="inlineStr">
         <is>
-          <t>PMP1269709</t>
+          <t>PMP1270089</t>
         </is>
       </c>
       <c r="E292" s="6" t="n">
-        <v>-846601</v>
+        <v>-160207</v>
       </c>
       <c r="F292" s="10" t="inlineStr">
         <is>
@@ -6897,11 +6897,11 @@
         </is>
       </c>
       <c r="H292" s="6" t="n">
-        <v>-846601</v>
+        <v>-160207</v>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269709</t>
+          <t>Rechazo PMP1270089</t>
         </is>
       </c>
     </row>
@@ -6913,11 +6913,11 @@
       </c>
       <c r="D293" s="10" t="inlineStr">
         <is>
-          <t>PMP1269710</t>
+          <t>PMP1270316</t>
         </is>
       </c>
       <c r="E293" s="6" t="n">
-        <v>-82421</v>
+        <v>-967638</v>
       </c>
       <c r="F293" s="10" t="inlineStr">
         <is>
@@ -6930,11 +6930,11 @@
         </is>
       </c>
       <c r="H293" s="6" t="n">
-        <v>-82421</v>
+        <v>-967638</v>
       </c>
       <c r="I293" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269710</t>
+          <t>Rechazo PMP1270316</t>
         </is>
       </c>
     </row>
@@ -6946,11 +6946,11 @@
       </c>
       <c r="D294" s="10" t="inlineStr">
         <is>
-          <t>PMP1269725</t>
+          <t>PMP1270345</t>
         </is>
       </c>
       <c r="E294" s="6" t="n">
-        <v>-19608</v>
+        <v>-195730</v>
       </c>
       <c r="F294" s="10" t="inlineStr">
         <is>
@@ -6963,11 +6963,11 @@
         </is>
       </c>
       <c r="H294" s="6" t="n">
-        <v>-19608</v>
+        <v>-195730</v>
       </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269725</t>
+          <t>Rechazo PMP1270345</t>
         </is>
       </c>
     </row>
@@ -6979,11 +6979,11 @@
       </c>
       <c r="D295" s="10" t="inlineStr">
         <is>
-          <t>PMP1269740</t>
+          <t>PMP1270348</t>
         </is>
       </c>
       <c r="E295" s="6" t="n">
-        <v>-887036</v>
+        <v>-183603</v>
       </c>
       <c r="F295" s="10" t="inlineStr">
         <is>
@@ -6996,11 +6996,11 @@
         </is>
       </c>
       <c r="H295" s="6" t="n">
-        <v>-887036</v>
+        <v>-183603</v>
       </c>
       <c r="I295" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269740</t>
+          <t>Rechazo PMP1270348</t>
         </is>
       </c>
     </row>
@@ -7012,11 +7012,11 @@
       </c>
       <c r="D296" s="10" t="inlineStr">
         <is>
-          <t>PMP1269787</t>
+          <t>PMP1270354</t>
         </is>
       </c>
       <c r="E296" s="6" t="n">
-        <v>-279182</v>
+        <v>-80127</v>
       </c>
       <c r="F296" s="10" t="inlineStr">
         <is>
@@ -7029,11 +7029,11 @@
         </is>
       </c>
       <c r="H296" s="6" t="n">
-        <v>-279182</v>
+        <v>-80127</v>
       </c>
       <c r="I296" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269787</t>
+          <t>Rechazo PMP1270354</t>
         </is>
       </c>
     </row>
@@ -7045,11 +7045,11 @@
       </c>
       <c r="D297" s="10" t="inlineStr">
         <is>
-          <t>PMP1269999</t>
+          <t>PMP1270549</t>
         </is>
       </c>
       <c r="E297" s="6" t="n">
-        <v>-87001</v>
+        <v>-421424</v>
       </c>
       <c r="F297" s="10" t="inlineStr">
         <is>
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="H297" s="6" t="n">
-        <v>-87001</v>
+        <v>-421424</v>
       </c>
       <c r="I297" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1269999</t>
+          <t>Rechazo PMP1270549</t>
         </is>
       </c>
     </row>
@@ -7078,11 +7078,11 @@
       </c>
       <c r="D298" s="10" t="inlineStr">
         <is>
-          <t>PMP1270057</t>
+          <t>PMP1270551</t>
         </is>
       </c>
       <c r="E298" s="6" t="n">
-        <v>-1980306</v>
+        <v>-93434</v>
       </c>
       <c r="F298" s="10" t="inlineStr">
         <is>
@@ -7095,11 +7095,11 @@
         </is>
       </c>
       <c r="H298" s="6" t="n">
-        <v>-1980306</v>
+        <v>-93434</v>
       </c>
       <c r="I298" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270057</t>
+          <t>Rechazo PMP1270551</t>
         </is>
       </c>
     </row>
@@ -7111,11 +7111,11 @@
       </c>
       <c r="D299" s="10" t="inlineStr">
         <is>
-          <t>PMP1270059</t>
+          <t>PMP1270696</t>
         </is>
       </c>
       <c r="E299" s="6" t="n">
-        <v>-1091682</v>
+        <v>-177716</v>
       </c>
       <c r="F299" s="10" t="inlineStr">
         <is>
@@ -7128,11 +7128,11 @@
         </is>
       </c>
       <c r="H299" s="6" t="n">
-        <v>-1091682</v>
+        <v>-177716</v>
       </c>
       <c r="I299" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270059</t>
+          <t>Rechazo PMP1270696</t>
         </is>
       </c>
     </row>
@@ -7144,11 +7144,11 @@
       </c>
       <c r="D300" s="10" t="inlineStr">
         <is>
-          <t>PMP1270062</t>
+          <t>PMP1271253</t>
         </is>
       </c>
       <c r="E300" s="6" t="n">
-        <v>-107500</v>
+        <v>-186541</v>
       </c>
       <c r="F300" s="10" t="inlineStr">
         <is>
@@ -7161,11 +7161,11 @@
         </is>
       </c>
       <c r="H300" s="6" t="n">
-        <v>-107500</v>
+        <v>-186541</v>
       </c>
       <c r="I300" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270062</t>
+          <t>Rechazo PMP1271253</t>
         </is>
       </c>
     </row>
@@ -7177,28 +7177,28 @@
       </c>
       <c r="D301" s="10" t="inlineStr">
         <is>
-          <t>PMP1270069</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E301" s="6" t="n">
-        <v>-1769895</v>
+        <v>-161133</v>
       </c>
       <c r="F301" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G301" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H301" s="6" t="n">
-        <v>-1769895</v>
+        <v>-161133</v>
       </c>
       <c r="I301" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270069</t>
+          <t>DCA DSCTO 20.251.200.196.186 DESCUENTO CALENDARI PERFUME</t>
         </is>
       </c>
     </row>
@@ -7210,28 +7210,28 @@
       </c>
       <c r="D302" s="10" t="inlineStr">
         <is>
-          <t>PMP1270070</t>
+          <t>DESCUENTO COMPRAS</t>
         </is>
       </c>
       <c r="E302" s="6" t="n">
-        <v>-35598445</v>
+        <v>-582054</v>
       </c>
       <c r="F302" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G302" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H302" s="6" t="n">
-        <v>-35598445</v>
+        <v>-582054</v>
       </c>
       <c r="I302" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270070</t>
+          <t>DCC DSCTO 20.222.600.126.372 DESCUENTO COMPRAS PLATOS</t>
         </is>
       </c>
     </row>
@@ -7243,28 +7243,28 @@
       </c>
       <c r="D303" s="10" t="inlineStr">
         <is>
-          <t>PMP1270075</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E303" s="6" t="n">
-        <v>-1063192</v>
+        <v>-6240707</v>
       </c>
       <c r="F303" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G303" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H303" s="6" t="n">
-        <v>-1063192</v>
+        <v>-6240707</v>
       </c>
       <c r="I303" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270075</t>
+          <t>DND DSCTO 20.171.100.014.225 DEVOLUCIONES DROGUE</t>
         </is>
       </c>
     </row>
@@ -7276,28 +7276,28 @@
       </c>
       <c r="D304" s="10" t="inlineStr">
         <is>
-          <t>PMP1270081</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E304" s="6" t="n">
-        <v>-287167</v>
+        <v>-479755</v>
       </c>
       <c r="F304" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G304" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H304" s="6" t="n">
-        <v>-287167</v>
+        <v>-479755</v>
       </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270081</t>
+          <t>DND DSCTO 20.181.100.045.651 DEVOLUCIONES DROGUE</t>
         </is>
       </c>
     </row>
@@ -7309,28 +7309,28 @@
       </c>
       <c r="D305" s="10" t="inlineStr">
         <is>
-          <t>PMP1270089</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E305" s="6" t="n">
-        <v>-160207</v>
+        <v>-4357583</v>
       </c>
       <c r="F305" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G305" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H305" s="6" t="n">
-        <v>-160207</v>
+        <v>-4357583</v>
       </c>
       <c r="I305" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270089</t>
+          <t>DND DSCTO 20.171.200.014.220 DEVOLUCIONES PERFUME</t>
         </is>
       </c>
     </row>
@@ -7342,28 +7342,28 @@
       </c>
       <c r="D306" s="10" t="inlineStr">
         <is>
-          <t>PMP1270316</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E306" s="6" t="n">
-        <v>-967638</v>
+        <v>-72808231</v>
       </c>
       <c r="F306" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G306" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H306" s="6" t="n">
-        <v>-967638</v>
+        <v>-72808231</v>
       </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270316</t>
+          <t>DCF DSCTO 20.171.100.014.225 DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -7375,28 +7375,28 @@
       </c>
       <c r="D307" s="10" t="inlineStr">
         <is>
-          <t>PMP1270345</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E307" s="6" t="n">
-        <v>-195730</v>
+        <v>-7813296</v>
       </c>
       <c r="F307" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G307" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H307" s="6" t="n">
-        <v>-195730</v>
+        <v>-7813296</v>
       </c>
       <c r="I307" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270345</t>
+          <t>DCF DSCTO 20.181.100.032.054 DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -7408,28 +7408,28 @@
       </c>
       <c r="D308" s="10" t="inlineStr">
         <is>
-          <t>PMP1270348</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E308" s="6" t="n">
-        <v>-183603</v>
+        <v>-8795517</v>
       </c>
       <c r="F308" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G308" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H308" s="6" t="n">
-        <v>-183603</v>
+        <v>-8795517</v>
       </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270348</t>
+          <t>DCF DSCTO 20.181.100.045.651 DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -7441,28 +7441,28 @@
       </c>
       <c r="D309" s="10" t="inlineStr">
         <is>
-          <t>PMP1270354</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E309" s="6" t="n">
-        <v>-80127</v>
+        <v>-101676935</v>
       </c>
       <c r="F309" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G309" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H309" s="6" t="n">
-        <v>-80127</v>
+        <v>-101676935</v>
       </c>
       <c r="I309" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270354</t>
+          <t>DCF DSCTO 20.171.200.014.220 DSTO COMERCIAL FIJO PERFUME</t>
         </is>
       </c>
     </row>
@@ -7474,28 +7474,28 @@
       </c>
       <c r="D310" s="10" t="inlineStr">
         <is>
-          <t>PMP1270549</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E310" s="6" t="n">
-        <v>-421424</v>
+        <v>-92620002</v>
       </c>
       <c r="F310" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G310" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H310" s="6" t="n">
-        <v>-421424</v>
+        <v>-92620002</v>
       </c>
       <c r="I310" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270549</t>
+          <t>DCF DSCTO 20.181.200.033.536 DSTO COMERCIAL FIJO PERFUME</t>
         </is>
       </c>
     </row>
@@ -7507,28 +7507,28 @@
       </c>
       <c r="D311" s="10" t="inlineStr">
         <is>
-          <t>PMP1270551</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E311" s="6" t="n">
-        <v>-93434</v>
+        <v>-8730793</v>
       </c>
       <c r="F311" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G311" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H311" s="6" t="n">
-        <v>-93434</v>
+        <v>-8730793</v>
       </c>
       <c r="I311" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270551</t>
+          <t>DCF DSCTO 20.222.600.126.372 DSTO COMERCIAL FIJO PLATOS</t>
         </is>
       </c>
     </row>
@@ -7540,28 +7540,28 @@
       </c>
       <c r="D312" s="10" t="inlineStr">
         <is>
-          <t>PMP1270696</t>
+          <t>VPP1 2004460</t>
         </is>
       </c>
       <c r="E312" s="6" t="n">
-        <v>-177716</v>
+        <v>-44982000</v>
       </c>
       <c r="F312" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G312" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H312" s="6" t="n">
-        <v>-177716</v>
+        <v>-44982000</v>
       </c>
       <c r="I312" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1270696</t>
+          <t>VPP1 2004460</t>
         </is>
       </c>
     </row>
@@ -7573,28 +7573,28 @@
       </c>
       <c r="D313" s="10" t="inlineStr">
         <is>
-          <t>PMP1271253</t>
+          <t>VPP2 2020050</t>
         </is>
       </c>
       <c r="E313" s="6" t="n">
-        <v>-186541</v>
+        <v>-376904211</v>
       </c>
       <c r="F313" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G313" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H313" s="6" t="n">
-        <v>-186541</v>
+        <v>-376904211</v>
       </c>
       <c r="I313" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1271253</t>
+          <t>VPP2 2020050</t>
         </is>
       </c>
     </row>
@@ -7606,28 +7606,28 @@
       </c>
       <c r="D314" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004460</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E314" s="6" t="n">
-        <v>-44982000</v>
+        <v>151.3599999413127</v>
       </c>
       <c r="F314" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G314" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H314" s="6" t="n">
-        <v>-44982000</v>
+        <v>151.3599999413127</v>
       </c>
       <c r="I314" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004460</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -7639,28 +7639,28 @@
       </c>
       <c r="D315" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2020050</t>
+          <t>Costo de Transferen</t>
         </is>
       </c>
       <c r="E315" s="6" t="n">
-        <v>-376904211</v>
+        <v>-3000</v>
       </c>
       <c r="F315" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Costo de Transferen</t>
         </is>
       </c>
       <c r="G315" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H315" s="6" t="n">
-        <v>-376904211</v>
+        <v>-3000</v>
       </c>
       <c r="I315" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2020050</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>

--- a/app/Archivos/Template/Template_HRC_Cenco.xlsx
+++ b/app/Archivos/Template/Template_HRC_Cenco.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I315"/>
+  <dimension ref="A1:I314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>9168890610.360001</v>
+        <v>9168890459</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>9168890610.360001</v>
+        <v>9168890459</v>
       </c>
     </row>
     <row r="9"/>
@@ -626,7 +626,7 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="21">
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="22">
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="23">
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="24">
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="25">
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="26">
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="27">
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="28">
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="29">
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -857,7 +857,7 @@
     <row r="30">
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="31">
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="32">
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="33">
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="34">
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -962,7 +962,7 @@
     <row r="35">
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="36">
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="37">
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="38">
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="39">
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="40">
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="41">
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="42">
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="43">
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="44">
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="45">
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="46">
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="47">
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="48">
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="49">
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="50">
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="51">
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="52">
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -1340,7 +1340,7 @@
     <row r="53">
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="54">
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="55">
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="56">
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="57">
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="58">
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="59">
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="60">
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="61">
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="64">
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="65">
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="66">
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="67">
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="68">
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="69">
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="70">
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -1718,7 +1718,7 @@
     <row r="71">
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="72">
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="73">
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="74">
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="75">
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="76">
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -1844,7 +1844,7 @@
     <row r="77">
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -1865,7 +1865,7 @@
     <row r="78">
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="79">
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="80">
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="81">
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="82">
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="83">
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="84">
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="85">
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -2033,7 +2033,7 @@
     <row r="86">
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -2054,7 +2054,7 @@
     <row r="87">
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="88">
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -2096,7 +2096,7 @@
     <row r="89">
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="90">
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="91">
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="92">
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="93">
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="94">
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -2222,7 +2222,7 @@
     <row r="95">
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="96">
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -2264,7 +2264,7 @@
     <row r="97">
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -2285,7 +2285,7 @@
     <row r="98">
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="99">
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="100">
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -2348,7 +2348,7 @@
     <row r="101">
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="102">
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="103">
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="104">
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -2432,7 +2432,7 @@
     <row r="105">
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="106">
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="107">
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="108">
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <row r="109">
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -2537,7 +2537,7 @@
     <row r="110">
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="111">
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="112">
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -2600,7 +2600,7 @@
     <row r="113">
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="114">
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -2642,7 +2642,7 @@
     <row r="115">
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="116">
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="117">
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -2705,7 +2705,7 @@
     <row r="118">
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -2726,7 +2726,7 @@
     <row r="119">
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="120">
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="121">
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -2789,7 +2789,7 @@
     <row r="122">
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -2810,7 +2810,7 @@
     <row r="123">
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="124">
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="125">
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="126">
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -2894,7 +2894,7 @@
     <row r="127">
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="128">
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -2936,7 +2936,7 @@
     <row r="129">
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="130">
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="131">
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="132">
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="133">
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="134">
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="135">
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="136">
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <row r="137">
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -3125,7 +3125,7 @@
     <row r="138">
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="139">
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="140">
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="141">
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="142">
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="143">
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="144">
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -3272,7 +3272,7 @@
     <row r="145">
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="146">
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -3314,7 +3314,7 @@
     <row r="147">
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="148">
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="149">
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="150">
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="151">
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="152">
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -3440,7 +3440,7 @@
     <row r="153">
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -3461,7 +3461,7 @@
     <row r="154">
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="155">
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
@@ -3503,7 +3503,7 @@
     <row r="156">
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="157">
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="158">
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="159">
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="160">
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="161">
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="162">
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
@@ -3650,7 +3650,7 @@
     <row r="163">
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="164">
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
@@ -3692,7 +3692,7 @@
     <row r="165">
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="166">
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="167">
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
@@ -3755,7 +3755,7 @@
     <row r="168">
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="169">
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
@@ -3797,7 +3797,7 @@
     <row r="170">
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
@@ -3818,7 +3818,7 @@
     <row r="171">
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
@@ -3839,7 +3839,7 @@
     <row r="172">
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="173">
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
@@ -3881,7 +3881,7 @@
     <row r="174">
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="175">
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
@@ -3923,7 +3923,7 @@
     <row r="176">
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="177">
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="178">
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="179">
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
@@ -4007,7 +4007,7 @@
     <row r="180">
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
@@ -4028,7 +4028,7 @@
     <row r="181">
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
@@ -4049,7 +4049,7 @@
     <row r="182">
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="183">
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="184">
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
@@ -4112,7 +4112,7 @@
     <row r="185">
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
@@ -4133,7 +4133,7 @@
     <row r="186">
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
@@ -4154,7 +4154,7 @@
     <row r="187">
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
@@ -4175,7 +4175,7 @@
     <row r="188">
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="189">
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
@@ -4217,7 +4217,7 @@
     <row r="190">
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="191">
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="192">
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
@@ -4280,7 +4280,7 @@
     <row r="193">
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="194">
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="195">
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="196">
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="197">
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
@@ -4385,7 +4385,7 @@
     <row r="198">
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="199">
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="200">
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="201">
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="202">
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
@@ -4490,7 +4490,7 @@
     <row r="203">
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
@@ -4511,7 +4511,7 @@
     <row r="204">
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
@@ -4532,7 +4532,7 @@
     <row r="205">
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
@@ -4553,7 +4553,7 @@
     <row r="206">
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="207">
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="208">
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="209">
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="210">
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="211">
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="212">
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="213">
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="214">
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
@@ -4742,7 +4742,7 @@
     <row r="215">
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
@@ -4763,7 +4763,7 @@
     <row r="216">
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="217">
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="218">
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
@@ -4826,7 +4826,7 @@
     <row r="219">
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="220">
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
@@ -4868,7 +4868,7 @@
     <row r="221">
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
@@ -4889,7 +4889,7 @@
     <row r="222">
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
@@ -4910,7 +4910,7 @@
     <row r="223">
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="224">
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="225">
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
@@ -4973,7 +4973,7 @@
     <row r="226">
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
@@ -4994,7 +4994,7 @@
     <row r="227">
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="228">
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="229">
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="230">
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="231">
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="232">
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
@@ -5120,7 +5120,7 @@
     <row r="233">
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
@@ -5141,7 +5141,7 @@
     <row r="234">
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="235">
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
@@ -5183,7 +5183,7 @@
     <row r="236">
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
@@ -5204,7 +5204,7 @@
     <row r="237">
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
@@ -5225,7 +5225,7 @@
     <row r="238">
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="239">
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
@@ -5267,7 +5267,7 @@
     <row r="240">
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
@@ -5288,7 +5288,7 @@
     <row r="241">
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="242">
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
@@ -5330,7 +5330,7 @@
     <row r="243">
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
@@ -5351,7 +5351,7 @@
     <row r="244">
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D244" s="10" t="inlineStr">
@@ -5372,7 +5372,7 @@
     <row r="245">
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="246">
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
@@ -5414,7 +5414,7 @@
     <row r="247">
       <c r="C247" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
@@ -5435,7 +5435,7 @@
     <row r="248">
       <c r="C248" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>FACTURA PROVEEDOR</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
@@ -7606,59 +7606,26 @@
       </c>
       <c r="D314" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Costo de Transferen</t>
         </is>
       </c>
       <c r="E314" s="6" t="n">
-        <v>151.3599999413127</v>
+        <v>-3000</v>
       </c>
       <c r="F314" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Costo de Transferen</t>
         </is>
       </c>
       <c r="G314" s="10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H314" s="6" t="n">
-        <v>151.3599999413127</v>
+        <v>-3000</v>
       </c>
       <c r="I314" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="C315" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos no asociados a FC</t>
-        </is>
-      </c>
-      <c r="D315" s="10" t="inlineStr">
-        <is>
-          <t>Costo de Transferen</t>
-        </is>
-      </c>
-      <c r="E315" s="6" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="F315" s="10" t="inlineStr">
-        <is>
-          <t>Costo de Transferen</t>
-        </is>
-      </c>
-      <c r="G315" s="10" t="inlineStr">
-        <is>
-          <t>WOB</t>
-        </is>
-      </c>
-      <c r="H315" s="6" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="I315" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>
